--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39D4995-03BB-4DBC-AD00-6E7DF2FB8F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5541FD29-BC27-4C34-BE59-09FD0064C79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="12660" yWindow="-21710" windowWidth="38620" windowHeight="21360" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="333">
   <si>
     <t>BGC10</t>
   </si>
@@ -888,9 +888,6 @@
     <t>KMG36</t>
   </si>
   <si>
-    <t>WO32oz</t>
-  </si>
-  <si>
     <t>WSPRO2pk</t>
   </si>
   <si>
@@ -906,10 +903,127 @@
     <t>Ovala-42</t>
   </si>
   <si>
-    <t>Orgil</t>
-  </si>
-  <si>
     <t>ACE Hardware</t>
+  </si>
+  <si>
+    <t>Lotus Light</t>
+  </si>
+  <si>
+    <t>Olla</t>
+  </si>
+  <si>
+    <t>.25oz lip tube</t>
+  </si>
+  <si>
+    <t>2 oz</t>
+  </si>
+  <si>
+    <t>5 oz</t>
+  </si>
+  <si>
+    <t>Multi Purpose 3 oz</t>
+  </si>
+  <si>
+    <t>Calming 3 oz</t>
+  </si>
+  <si>
+    <t>Beautifying Mud 3oz</t>
+  </si>
+  <si>
+    <t>Clarifying Mud 3 oz</t>
+  </si>
+  <si>
+    <t>Detoxifying Mud 3 oz</t>
+  </si>
+  <si>
+    <t>Waxelene</t>
+  </si>
+  <si>
+    <t>Orgill</t>
+  </si>
+  <si>
+    <t>VP2-RHP-2</t>
+  </si>
+  <si>
+    <t>VP5-RHP-5</t>
+  </si>
+  <si>
+    <t>VP10-RHP-5</t>
+  </si>
+  <si>
+    <t>VP12-RHP-12</t>
+  </si>
+  <si>
+    <t>Rainhandler</t>
+  </si>
+  <si>
+    <t>SLBottle</t>
+  </si>
+  <si>
+    <t>SLBoxB</t>
+  </si>
+  <si>
+    <t>SLBoxW</t>
+  </si>
+  <si>
+    <t>Safer Lock</t>
+  </si>
+  <si>
+    <t>PPMST5</t>
+  </si>
+  <si>
+    <t>PPMST50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHDE-2 </t>
+  </si>
+  <si>
+    <t>RHP-5</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>RHDE-2 VP5</t>
+  </si>
+  <si>
+    <t>BluFix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11-1-26-32 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-1-26-01 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21-2-26-00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21-2-36-00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22-2-26-00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22-2-36-00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-2-26-00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-2-26-00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27-2-26-00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27-2-36-00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">44-2-30-00 </t>
+  </si>
+  <si>
+    <t>FF10oz</t>
   </si>
 </sst>
 </file>
@@ -1307,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K614"/>
+  <dimension ref="A1:K681"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -2150,7 +2264,7 @@
         <v>19.95</v>
       </c>
       <c r="D56" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K56" s="3"/>
     </row>
@@ -2165,7 +2279,7 @@
         <v>19.95</v>
       </c>
       <c r="D57" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K57" s="3"/>
     </row>
@@ -2180,7 +2294,7 @@
         <v>19.95</v>
       </c>
       <c r="D58" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K58" s="3"/>
     </row>
@@ -2195,7 +2309,7 @@
         <v>19.95</v>
       </c>
       <c r="D59" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K59" s="3"/>
     </row>
@@ -2210,7 +2324,7 @@
         <v>19.95</v>
       </c>
       <c r="D60" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K60" s="3"/>
     </row>
@@ -2225,7 +2339,7 @@
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K61" s="3"/>
     </row>
@@ -2240,7 +2354,7 @@
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K62" s="3"/>
     </row>
@@ -2528,7 +2642,7 @@
         <v>156</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C81" s="6">
         <v>164</v>
@@ -2923,42 +3037,42 @@
       <c r="A108" t="s">
         <v>156</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C108" s="2">
-        <v>16.5</v>
+      <c r="B108" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C108" s="6">
+        <v>5.5</v>
       </c>
       <c r="D108" t="s">
         <v>146</v>
       </c>
-      <c r="E108" s="1"/>
-      <c r="K108" s="1"/>
+      <c r="K108" s="3"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>156</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C109" s="6">
-        <v>22</v>
+      <c r="B109" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C109" s="2">
+        <v>16.5</v>
       </c>
       <c r="D109" t="s">
         <v>146</v>
       </c>
-      <c r="K109" s="3"/>
+      <c r="E109" s="1"/>
+      <c r="K109" s="1"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>156</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C110" s="6">
-        <v>26.25</v>
+        <v>22</v>
       </c>
       <c r="D110" t="s">
         <v>146</v>
@@ -2970,10 +3084,10 @@
         <v>156</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C111" s="6">
-        <v>28</v>
+        <v>26.25</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -2985,10 +3099,10 @@
         <v>156</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C112" s="6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D112" t="s">
         <v>146</v>
@@ -2999,27 +3113,26 @@
       <c r="A113" t="s">
         <v>156</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C113" s="2">
-        <v>25</v>
+      <c r="B113" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C113" s="6">
+        <v>26</v>
       </c>
       <c r="D113" t="s">
         <v>146</v>
       </c>
-      <c r="E113" s="1"/>
-      <c r="K113" s="1"/>
+      <c r="K113" s="3"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>156</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C114" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D114" t="s">
         <v>146</v>
@@ -3032,13 +3145,13 @@
         <v>156</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C115" s="2">
-        <v>1149.73</v>
+        <v>12</v>
       </c>
       <c r="D115" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E115" s="1"/>
       <c r="K115" s="1"/>
@@ -3048,10 +3161,10 @@
         <v>156</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C116" s="2">
-        <v>919.63</v>
+        <v>1149.73</v>
       </c>
       <c r="D116" t="s">
         <v>147</v>
@@ -3064,10 +3177,10 @@
         <v>156</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C117" s="2">
-        <v>1188.08</v>
+        <v>919.63</v>
       </c>
       <c r="D117" t="s">
         <v>147</v>
@@ -3080,10 +3193,10 @@
         <v>156</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C118" s="2">
-        <v>1149.73</v>
+        <v>1188.08</v>
       </c>
       <c r="D118" t="s">
         <v>147</v>
@@ -3096,10 +3209,10 @@
         <v>156</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C119" s="2">
-        <v>957.98</v>
+        <v>1149.73</v>
       </c>
       <c r="D119" t="s">
         <v>147</v>
@@ -3112,10 +3225,10 @@
         <v>156</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C120" s="2">
-        <v>919.63</v>
+        <v>957.98</v>
       </c>
       <c r="D120" t="s">
         <v>147</v>
@@ -3128,10 +3241,10 @@
         <v>156</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C121" s="2">
-        <v>1571.58</v>
+        <v>919.63</v>
       </c>
       <c r="D121" t="s">
         <v>147</v>
@@ -3143,26 +3256,27 @@
       <c r="A122" t="s">
         <v>156</v>
       </c>
-      <c r="B122" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C122" s="6">
-        <v>1533.23</v>
+      <c r="B122" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C122" s="2">
+        <v>1571.58</v>
       </c>
       <c r="D122" t="s">
         <v>147</v>
       </c>
-      <c r="K122" s="3"/>
+      <c r="E122" s="1"/>
+      <c r="K122" s="1"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>156</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C123" s="6">
-        <v>1571.58</v>
+        <v>1533.23</v>
       </c>
       <c r="D123" t="s">
         <v>147</v>
@@ -3174,10 +3288,10 @@
         <v>156</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C124" s="6">
-        <v>1533.23</v>
+        <v>1571.58</v>
       </c>
       <c r="D124" t="s">
         <v>147</v>
@@ -3189,10 +3303,10 @@
         <v>156</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C125" s="6">
-        <v>758.56</v>
+        <v>1533.23</v>
       </c>
       <c r="D125" t="s">
         <v>147</v>
@@ -3204,10 +3318,10 @@
         <v>156</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C126" s="6">
-        <v>689</v>
+        <v>758.56</v>
       </c>
       <c r="D126" t="s">
         <v>147</v>
@@ -3219,10 +3333,10 @@
         <v>156</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C127" s="6">
-        <v>421.08</v>
+        <v>689</v>
       </c>
       <c r="D127" t="s">
         <v>147</v>
@@ -3234,10 +3348,10 @@
         <v>156</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C128" s="6">
-        <v>382.73</v>
+        <v>421.08</v>
       </c>
       <c r="D128" t="s">
         <v>147</v>
@@ -3249,10 +3363,10 @@
         <v>156</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C129" s="6">
-        <v>574.48</v>
+        <v>382.73</v>
       </c>
       <c r="D129" t="s">
         <v>147</v>
@@ -3264,10 +3378,10 @@
         <v>156</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C130" s="6">
-        <v>536.13</v>
+        <v>574.48</v>
       </c>
       <c r="D130" t="s">
         <v>147</v>
@@ -3279,10 +3393,10 @@
         <v>156</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C131" s="6">
-        <v>87</v>
+        <v>536.13</v>
       </c>
       <c r="D131" t="s">
         <v>147</v>
@@ -3294,10 +3408,10 @@
         <v>156</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C132" s="6">
-        <v>225</v>
+        <v>87</v>
       </c>
       <c r="D132" t="s">
         <v>147</v>
@@ -3309,10 +3423,10 @@
         <v>156</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C133" s="6">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="D133" t="s">
         <v>147</v>
@@ -3324,13 +3438,13 @@
         <v>156</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C134" s="6">
-        <v>69.900000000000006</v>
+        <v>149</v>
       </c>
       <c r="D134" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K134" s="3"/>
     </row>
@@ -3354,10 +3468,10 @@
         <v>156</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>94</v>
+        <v>314</v>
       </c>
       <c r="C136" s="6">
-        <v>6.25</v>
+        <v>16</v>
       </c>
       <c r="D136" t="s">
         <v>148</v>
@@ -3369,10 +3483,10 @@
         <v>156</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>95</v>
+        <v>315</v>
       </c>
       <c r="C137" s="6">
-        <v>6.75</v>
+        <v>33</v>
       </c>
       <c r="D137" t="s">
         <v>148</v>
@@ -3383,11 +3497,11 @@
       <c r="A138" t="s">
         <v>156</v>
       </c>
-      <c r="B138" s="3">
-        <v>4430</v>
+      <c r="B138" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="C138" s="6">
-        <v>15.25</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="D138" t="s">
         <v>148</v>
@@ -3398,11 +3512,11 @@
       <c r="A139" t="s">
         <v>156</v>
       </c>
-      <c r="B139" s="3">
-        <v>4442</v>
+      <c r="B139" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C139" s="6">
-        <v>18.899999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="D139" t="s">
         <v>148</v>
@@ -3414,10 +3528,10 @@
         <v>156</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C140" s="6">
-        <v>224</v>
+        <v>6.75</v>
       </c>
       <c r="D140" t="s">
         <v>148</v>
@@ -3428,11 +3542,11 @@
       <c r="A141" t="s">
         <v>156</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>97</v>
+      <c r="B141" s="3">
+        <v>4430</v>
       </c>
       <c r="C141" s="6">
-        <v>972</v>
+        <v>15.25</v>
       </c>
       <c r="D141" t="s">
         <v>148</v>
@@ -3444,10 +3558,10 @@
         <v>156</v>
       </c>
       <c r="B142" s="3">
-        <v>4642</v>
+        <v>4442</v>
       </c>
       <c r="C142" s="6">
-        <v>20.8</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D142" t="s">
         <v>148</v>
@@ -3459,10 +3573,10 @@
         <v>156</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C143" s="6">
-        <v>126</v>
+        <v>224</v>
       </c>
       <c r="D143" t="s">
         <v>148</v>
@@ -3473,11 +3587,11 @@
       <c r="A144" t="s">
         <v>156</v>
       </c>
-      <c r="B144" s="3">
-        <v>4660</v>
+      <c r="B144" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="C144" s="6">
-        <v>24.7</v>
+        <v>972</v>
       </c>
       <c r="D144" t="s">
         <v>148</v>
@@ -3489,10 +3603,10 @@
         <v>156</v>
       </c>
       <c r="B145" s="3">
-        <v>6630</v>
+        <v>4642</v>
       </c>
       <c r="C145" s="6">
-        <v>19</v>
+        <v>20.8</v>
       </c>
       <c r="D145" t="s">
         <v>148</v>
@@ -3503,11 +3617,11 @@
       <c r="A146" t="s">
         <v>156</v>
       </c>
-      <c r="B146" s="3">
-        <v>6642</v>
+      <c r="B146" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="C146" s="6">
-        <v>26.8</v>
+        <v>126</v>
       </c>
       <c r="D146" t="s">
         <v>148</v>
@@ -3518,11 +3632,11 @@
       <c r="A147" t="s">
         <v>156</v>
       </c>
-      <c r="B147" s="3" t="s">
-        <v>99</v>
+      <c r="B147" s="3">
+        <v>4660</v>
       </c>
       <c r="C147" s="6">
-        <v>151.19999999999999</v>
+        <v>24.7</v>
       </c>
       <c r="D147" t="s">
         <v>148</v>
@@ -3534,10 +3648,10 @@
         <v>156</v>
       </c>
       <c r="B148" s="3">
-        <v>6660</v>
+        <v>6630</v>
       </c>
       <c r="C148" s="6">
-        <v>27.05</v>
+        <v>19</v>
       </c>
       <c r="D148" t="s">
         <v>148</v>
@@ -3548,11 +3662,11 @@
       <c r="A149" t="s">
         <v>156</v>
       </c>
-      <c r="B149" s="3" t="s">
-        <v>100</v>
+      <c r="B149" s="3">
+        <v>6642</v>
       </c>
       <c r="C149" s="6">
-        <v>160</v>
+        <v>26.8</v>
       </c>
       <c r="D149" t="s">
         <v>148</v>
@@ -3563,11 +3677,11 @@
       <c r="A150" t="s">
         <v>156</v>
       </c>
-      <c r="B150" s="3">
-        <v>8860</v>
+      <c r="B150" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C150" s="6">
-        <v>42.25</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="D150" t="s">
         <v>148</v>
@@ -3578,14 +3692,14 @@
       <c r="A151" t="s">
         <v>156</v>
       </c>
-      <c r="B151" s="3" t="s">
-        <v>101</v>
+      <c r="B151" s="3">
+        <v>6660</v>
       </c>
       <c r="C151" s="6">
-        <v>30.5</v>
+        <v>27.05</v>
       </c>
       <c r="D151" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K151" s="3"/>
     </row>
@@ -3594,13 +3708,13 @@
         <v>156</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C152" s="6">
-        <v>62</v>
+        <v>160</v>
       </c>
       <c r="D152" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K152" s="3"/>
     </row>
@@ -3608,14 +3722,14 @@
       <c r="A153" t="s">
         <v>156</v>
       </c>
-      <c r="B153" s="3" t="s">
-        <v>103</v>
+      <c r="B153" s="3">
+        <v>8860</v>
       </c>
       <c r="C153" s="6">
-        <v>79</v>
+        <v>42.25</v>
       </c>
       <c r="D153" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K153" s="3"/>
     </row>
@@ -3623,349 +3737,346 @@
       <c r="A154" t="s">
         <v>156</v>
       </c>
-      <c r="B154" t="s">
-        <v>258</v>
+      <c r="B154" s="3" t="s">
+        <v>319</v>
       </c>
       <c r="C154" s="6">
-        <v>10.85</v>
+        <v>22.85</v>
       </c>
       <c r="D154" t="s">
-        <v>270</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="K154" s="3"/>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>156</v>
       </c>
-      <c r="B155" t="s">
-        <v>259</v>
+      <c r="B155" s="3" t="s">
+        <v>317</v>
       </c>
       <c r="C155" s="6">
-        <v>10.85</v>
+        <v>15.75</v>
       </c>
       <c r="D155" t="s">
-        <v>270</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="K155" s="3"/>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>156</v>
       </c>
-      <c r="B156" t="s">
-        <v>260</v>
+      <c r="B156" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="C156" s="6">
-        <v>9.15</v>
+        <v>10.5</v>
       </c>
       <c r="D156" t="s">
-        <v>270</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="K156" s="3"/>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>156</v>
       </c>
-      <c r="B157" t="s">
-        <v>261</v>
+      <c r="B157" s="3" t="s">
+        <v>305</v>
       </c>
       <c r="C157" s="6">
-        <v>11.5</v>
+        <v>45</v>
       </c>
       <c r="D157" t="s">
-        <v>270</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="K157" s="3"/>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>156</v>
       </c>
-      <c r="B158" t="s">
-        <v>262</v>
+      <c r="B158" s="3" t="s">
+        <v>306</v>
       </c>
       <c r="C158" s="6">
-        <v>9.15</v>
+        <v>77.5</v>
       </c>
       <c r="D158" t="s">
-        <v>270</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="K158" s="3"/>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>156</v>
       </c>
-      <c r="B159" t="s">
-        <v>263</v>
+      <c r="B159" s="3" t="s">
+        <v>307</v>
       </c>
       <c r="C159" s="6">
-        <v>11.5</v>
+        <v>152.30000000000001</v>
       </c>
       <c r="D159" t="s">
-        <v>270</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="K159" s="3"/>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>156</v>
       </c>
-      <c r="B160" t="s">
-        <v>264</v>
+      <c r="B160" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="C160" s="6">
-        <v>11.5</v>
+        <v>273</v>
       </c>
       <c r="D160" t="s">
-        <v>270</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="K160" s="3"/>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>156</v>
       </c>
-      <c r="B161" t="s">
-        <v>265</v>
+      <c r="B161" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="C161" s="6">
-        <v>11.5</v>
+        <v>30.5</v>
       </c>
       <c r="D161" t="s">
-        <v>270</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="K161" s="3"/>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>156</v>
       </c>
-      <c r="B162" t="s">
-        <v>266</v>
+      <c r="B162" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="C162" s="6">
-        <v>11.15</v>
+        <v>62</v>
       </c>
       <c r="D162" t="s">
-        <v>270</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="K162" s="3"/>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>156</v>
       </c>
-      <c r="B163" t="s">
-        <v>267</v>
+      <c r="B163" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="C163" s="6">
-        <v>23.1</v>
+        <v>79</v>
       </c>
       <c r="D163" t="s">
-        <v>270</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="K163" s="3"/>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>156</v>
       </c>
-      <c r="B164" s="5" t="s">
-        <v>104</v>
+      <c r="B164" t="s">
+        <v>258</v>
       </c>
       <c r="C164" s="6">
-        <v>42</v>
+        <v>10.85</v>
       </c>
       <c r="D164" t="s">
-        <v>150</v>
-      </c>
-      <c r="K164" s="3"/>
+        <v>270</v>
+      </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>156</v>
       </c>
-      <c r="B165" s="3" t="s">
-        <v>105</v>
+      <c r="B165" t="s">
+        <v>259</v>
       </c>
       <c r="C165" s="6">
-        <v>68.25</v>
+        <v>10.85</v>
       </c>
       <c r="D165" t="s">
-        <v>151</v>
-      </c>
-      <c r="K165" s="3"/>
+        <v>270</v>
+      </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>156</v>
       </c>
-      <c r="B166" s="3" t="s">
-        <v>106</v>
+      <c r="B166" t="s">
+        <v>260</v>
       </c>
       <c r="C166" s="6">
-        <v>23.5</v>
+        <v>9.15</v>
       </c>
       <c r="D166" t="s">
-        <v>151</v>
-      </c>
-      <c r="K166" s="3"/>
+        <v>270</v>
+      </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>156</v>
       </c>
-      <c r="B167" s="3" t="s">
-        <v>107</v>
+      <c r="B167" t="s">
+        <v>261</v>
       </c>
       <c r="C167" s="6">
-        <v>21.5</v>
+        <v>11.5</v>
       </c>
       <c r="D167" t="s">
-        <v>152</v>
-      </c>
-      <c r="K167" s="3"/>
+        <v>270</v>
+      </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>156</v>
       </c>
-      <c r="B168" s="3" t="s">
-        <v>108</v>
+      <c r="B168" t="s">
+        <v>262</v>
       </c>
       <c r="C168" s="6">
-        <v>22.5</v>
+        <v>9.15</v>
       </c>
       <c r="D168" t="s">
-        <v>152</v>
-      </c>
-      <c r="K168" s="3"/>
+        <v>270</v>
+      </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>156</v>
       </c>
-      <c r="B169" s="3" t="s">
-        <v>109</v>
+      <c r="B169" t="s">
+        <v>263</v>
       </c>
       <c r="C169" s="6">
-        <v>25.9</v>
+        <v>11.5</v>
       </c>
       <c r="D169" t="s">
-        <v>152</v>
-      </c>
-      <c r="K169" s="3"/>
+        <v>270</v>
+      </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>156</v>
       </c>
-      <c r="B170" s="3" t="s">
-        <v>110</v>
+      <c r="B170" t="s">
+        <v>264</v>
       </c>
       <c r="C170" s="6">
-        <v>25.9</v>
+        <v>11.5</v>
       </c>
       <c r="D170" t="s">
-        <v>152</v>
-      </c>
-      <c r="K170" s="3"/>
+        <v>270</v>
+      </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>156</v>
       </c>
-      <c r="B171" s="3" t="s">
-        <v>111</v>
+      <c r="B171" t="s">
+        <v>265</v>
       </c>
       <c r="C171" s="6">
-        <v>25.9</v>
+        <v>11.5</v>
       </c>
       <c r="D171" t="s">
-        <v>152</v>
-      </c>
-      <c r="K171" s="3"/>
+        <v>270</v>
+      </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>156</v>
       </c>
-      <c r="B172" s="3" t="s">
-        <v>112</v>
+      <c r="B172" t="s">
+        <v>266</v>
       </c>
       <c r="C172" s="6">
-        <v>25.9</v>
+        <v>11.15</v>
       </c>
       <c r="D172" t="s">
-        <v>152</v>
-      </c>
-      <c r="K172" s="3"/>
+        <v>270</v>
+      </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>156</v>
       </c>
-      <c r="B173" s="3" t="s">
-        <v>113</v>
+      <c r="B173" t="s">
+        <v>267</v>
       </c>
       <c r="C173" s="6">
-        <v>25.9</v>
+        <v>23.1</v>
       </c>
       <c r="D173" t="s">
-        <v>152</v>
-      </c>
-      <c r="K173" s="3"/>
+        <v>270</v>
+      </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>156</v>
       </c>
-      <c r="B174" s="3" t="s">
-        <v>114</v>
+      <c r="B174" t="s">
+        <v>310</v>
       </c>
       <c r="C174" s="6">
-        <v>25.9</v>
+        <v>9.25</v>
       </c>
       <c r="D174" t="s">
-        <v>152</v>
-      </c>
-      <c r="K174" s="3"/>
+        <v>313</v>
+      </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>156</v>
       </c>
-      <c r="B175" s="3" t="s">
-        <v>115</v>
+      <c r="B175" t="s">
+        <v>311</v>
       </c>
       <c r="C175" s="6">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="D175" t="s">
-        <v>152</v>
-      </c>
-      <c r="K175" s="3"/>
+        <v>313</v>
+      </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>156</v>
       </c>
-      <c r="B176" s="3" t="s">
-        <v>116</v>
+      <c r="B176" t="s">
+        <v>312</v>
       </c>
       <c r="C176" s="6">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="D176" t="s">
-        <v>152</v>
-      </c>
-      <c r="K176" s="3"/>
+        <v>313</v>
+      </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>156</v>
       </c>
-      <c r="B177" s="3" t="s">
-        <v>117</v>
+      <c r="B177" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="C177" s="6">
-        <v>9.5</v>
+        <v>42</v>
       </c>
       <c r="D177" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K177" s="3"/>
     </row>
@@ -3974,13 +4085,13 @@
         <v>156</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C178" s="6">
-        <v>23.15</v>
+        <v>68.25</v>
       </c>
       <c r="D178" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K178" s="3"/>
     </row>
@@ -3989,13 +4100,13 @@
         <v>156</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C179" s="6">
-        <v>42.65</v>
+        <v>23.5</v>
       </c>
       <c r="D179" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K179" s="3"/>
     </row>
@@ -4004,13 +4115,13 @@
         <v>156</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C180" s="6">
-        <v>82</v>
+        <v>21.5</v>
       </c>
       <c r="D180" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K180" s="3"/>
     </row>
@@ -4019,13 +4130,13 @@
         <v>156</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C181" s="6">
-        <v>33.5</v>
+        <v>22.5</v>
       </c>
       <c r="D181" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K181" s="3"/>
     </row>
@@ -4034,13 +4145,13 @@
         <v>156</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C182" s="6">
-        <v>60.9</v>
+        <v>25.9</v>
       </c>
       <c r="D182" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K182" s="3"/>
     </row>
@@ -4049,13 +4160,13 @@
         <v>156</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C183" s="6">
-        <v>118</v>
+        <v>25.9</v>
       </c>
       <c r="D183" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K183" s="3"/>
     </row>
@@ -4064,13 +4175,13 @@
         <v>156</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C184" s="6">
-        <v>16</v>
+        <v>25.9</v>
       </c>
       <c r="D184" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K184" s="3"/>
     </row>
@@ -4079,13 +4190,13 @@
         <v>156</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C185" s="6">
-        <v>16</v>
+        <v>25.9</v>
       </c>
       <c r="D185" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K185" s="3"/>
     </row>
@@ -4094,13 +4205,13 @@
         <v>156</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C186" s="6">
-        <v>21.32</v>
+        <v>25.9</v>
       </c>
       <c r="D186" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K186" s="3"/>
     </row>
@@ -4109,13 +4220,13 @@
         <v>156</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C187" s="6">
-        <v>27.5</v>
+        <v>25.9</v>
       </c>
       <c r="D187" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K187" s="3"/>
     </row>
@@ -4124,13 +4235,13 @@
         <v>156</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C188" s="6">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="D188" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K188" s="3"/>
     </row>
@@ -4139,13 +4250,13 @@
         <v>156</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C189" s="6">
-        <v>11.9</v>
+        <v>9.5</v>
       </c>
       <c r="D189" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K189" s="3"/>
     </row>
@@ -4154,13 +4265,13 @@
         <v>156</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C190" s="6">
-        <v>18.05</v>
+        <v>9.5</v>
       </c>
       <c r="D190" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K190" s="3"/>
     </row>
@@ -4169,13 +4280,13 @@
         <v>156</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C191" s="6">
-        <v>4.8499999999999996</v>
+        <v>23.15</v>
       </c>
       <c r="D191" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K191" s="3"/>
     </row>
@@ -4184,210 +4295,223 @@
         <v>156</v>
       </c>
       <c r="B192" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C192" s="6">
+        <v>42.65</v>
+      </c>
+      <c r="D192" t="s">
+        <v>153</v>
+      </c>
+      <c r="K192" s="3"/>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>156</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C193" s="6">
+        <v>82</v>
+      </c>
+      <c r="D193" t="s">
+        <v>153</v>
+      </c>
+      <c r="K193" s="3"/>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>156</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C194" s="6">
+        <v>33.5</v>
+      </c>
+      <c r="D194" t="s">
+        <v>153</v>
+      </c>
+      <c r="K194" s="3"/>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>156</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C195" s="6">
+        <v>60.9</v>
+      </c>
+      <c r="D195" t="s">
+        <v>153</v>
+      </c>
+      <c r="K195" s="3"/>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>156</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C196" s="6">
+        <v>118</v>
+      </c>
+      <c r="D196" t="s">
+        <v>153</v>
+      </c>
+      <c r="K196" s="3"/>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>156</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C197" s="6">
+        <v>16</v>
+      </c>
+      <c r="D197" t="s">
+        <v>153</v>
+      </c>
+      <c r="K197" s="3"/>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>156</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C198" s="6">
+        <v>16</v>
+      </c>
+      <c r="D198" t="s">
+        <v>153</v>
+      </c>
+      <c r="K198" s="3"/>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>156</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C199" s="6">
+        <v>21.32</v>
+      </c>
+      <c r="D199" t="s">
+        <v>153</v>
+      </c>
+      <c r="K199" s="3"/>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>156</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C200" s="6">
+        <v>27.5</v>
+      </c>
+      <c r="D200" t="s">
+        <v>154</v>
+      </c>
+      <c r="K200" s="3"/>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>156</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C201" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="D201" t="s">
+        <v>154</v>
+      </c>
+      <c r="K201" s="3"/>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>156</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C202" s="6">
+        <v>11.9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>154</v>
+      </c>
+      <c r="K202" s="3"/>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>156</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C203" s="6">
+        <v>18.05</v>
+      </c>
+      <c r="D203" t="s">
+        <v>154</v>
+      </c>
+      <c r="K203" s="3"/>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>156</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C204" s="6">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="D204" t="s">
+        <v>154</v>
+      </c>
+      <c r="K204" s="3"/>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>156</v>
+      </c>
+      <c r="B205" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C192" s="6">
+      <c r="C205" s="6">
         <v>8</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D205" t="s">
         <v>154</v>
       </c>
-      <c r="K192" s="3"/>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>157</v>
-      </c>
-      <c r="B196" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C196" s="6">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="D196" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>157</v>
-      </c>
-      <c r="B197" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C197" s="6">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="D197" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>157</v>
-      </c>
-      <c r="B198" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C198" s="6">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="D198" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>157</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C199" s="6">
-        <v>11.85</v>
-      </c>
-      <c r="D199" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>157</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C200" s="6">
-        <v>15.44</v>
-      </c>
-      <c r="D200" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>157</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C201" s="6">
-        <v>18.510000000000002</v>
-      </c>
-      <c r="D201" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>157</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C202" s="6">
-        <v>17</v>
-      </c>
-      <c r="D202" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>157</v>
-      </c>
-      <c r="B203" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C203" s="6">
-        <v>20.6</v>
-      </c>
-      <c r="D203" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>157</v>
-      </c>
-      <c r="B204" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C204" s="6">
-        <v>29.36</v>
-      </c>
-      <c r="D204" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>157</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C205" s="6">
-        <v>30.9</v>
-      </c>
-      <c r="D205" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>157</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C206" s="6">
-        <v>30.9</v>
-      </c>
-      <c r="D206" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>157</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C207" s="6">
-        <v>37.6</v>
-      </c>
-      <c r="D207" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>157</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C208" s="6">
-        <v>133</v>
-      </c>
-      <c r="D208" t="s">
-        <v>142</v>
-      </c>
+      <c r="K205" s="3"/>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>157</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C209" s="6">
-        <v>145</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="D209" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -4395,13 +4519,13 @@
         <v>157</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C210" s="6">
-        <v>133</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="D210" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -4409,13 +4533,13 @@
         <v>157</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C211" s="6">
-        <v>145</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="D211" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -4423,13 +4547,13 @@
         <v>157</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>30</v>
+        <v>158</v>
       </c>
       <c r="C212" s="6">
-        <v>192</v>
+        <v>11.85</v>
       </c>
       <c r="D212" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -4437,13 +4561,13 @@
         <v>157</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C213" s="6">
-        <v>230</v>
+        <v>15.44</v>
       </c>
       <c r="D213" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -4451,13 +4575,13 @@
         <v>157</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C214" s="6">
-        <v>292</v>
+        <v>18.510000000000002</v>
       </c>
       <c r="D214" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -4465,13 +4589,13 @@
         <v>157</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C215" s="6">
-        <v>262.64999999999998</v>
+        <v>17</v>
       </c>
       <c r="D215" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -4479,13 +4603,13 @@
         <v>157</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>34</v>
+        <v>159</v>
       </c>
       <c r="C216" s="6">
-        <v>272.95</v>
+        <v>20.6</v>
       </c>
       <c r="D216" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -4493,13 +4617,13 @@
         <v>157</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="C217" s="6">
+        <v>29.36</v>
+      </c>
+      <c r="D217" t="s">
         <v>136</v>
-      </c>
-      <c r="D217" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -4507,13 +4631,13 @@
         <v>157</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="C218" s="6">
-        <v>125</v>
+        <v>30.9</v>
       </c>
       <c r="D218" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -4521,13 +4645,13 @@
         <v>157</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>37</v>
+        <v>162</v>
       </c>
       <c r="C219" s="6">
-        <v>56</v>
+        <v>30.9</v>
       </c>
       <c r="D219" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -4535,13 +4659,13 @@
         <v>157</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>22</v>
+        <v>163</v>
       </c>
       <c r="C220" s="6">
-        <v>13</v>
+        <v>37.6</v>
       </c>
       <c r="D220" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -4549,13 +4673,13 @@
         <v>157</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C221" s="6">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="D221" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -4563,405 +4687,405 @@
         <v>157</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C222" s="6">
-        <v>450</v>
+        <v>145</v>
       </c>
       <c r="D222" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>157</v>
       </c>
-      <c r="B223" s="4">
-        <v>6102</v>
-      </c>
-      <c r="C223" s="8">
-        <v>23.86</v>
+      <c r="B223" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C223" s="6">
+        <v>133</v>
       </c>
       <c r="D223" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>157</v>
       </c>
-      <c r="B224" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C224" s="8">
-        <v>35.5</v>
+      <c r="B224" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C224" s="6">
+        <v>145</v>
       </c>
       <c r="D224" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>157</v>
       </c>
-      <c r="B225" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C225" s="8">
-        <v>32</v>
+      <c r="B225" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C225" s="6">
+        <v>192</v>
       </c>
       <c r="D225" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>157</v>
       </c>
-      <c r="B226" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C226" s="8">
-        <v>47</v>
+      <c r="B226" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C226" s="6">
+        <v>230</v>
       </c>
       <c r="D226" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>157</v>
       </c>
-      <c r="B227" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C227" s="8">
-        <v>53</v>
+      <c r="B227" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C227" s="6">
+        <v>292</v>
       </c>
       <c r="D227" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>157</v>
       </c>
-      <c r="B228" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C228" s="8">
-        <v>48</v>
+      <c r="B228" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C228" s="6">
+        <v>262.64999999999998</v>
       </c>
       <c r="D228" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>157</v>
       </c>
-      <c r="B229" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C229" s="8">
-        <v>70</v>
+      <c r="B229" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C229" s="6">
+        <v>272.95</v>
       </c>
       <c r="D229" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>157</v>
       </c>
-      <c r="B230" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="C230" s="8">
-        <v>43</v>
+      <c r="B230" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C230" s="6">
+        <v>136</v>
       </c>
       <c r="D230" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>157</v>
       </c>
-      <c r="B231" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C231" s="8">
-        <v>46</v>
+      <c r="B231" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C231" s="6">
+        <v>125</v>
       </c>
       <c r="D231" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>157</v>
       </c>
-      <c r="B232" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="C232" s="8">
-        <v>48</v>
+      <c r="B232" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C232" s="6">
+        <v>56</v>
       </c>
       <c r="D232" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>157</v>
       </c>
-      <c r="B233" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="C233" s="8">
-        <v>53</v>
+      <c r="B233" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C233" s="6">
+        <v>13</v>
       </c>
       <c r="D233" t="s">
-        <v>269</v>
+        <v>140</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>157</v>
       </c>
-      <c r="B234" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C234" s="8">
-        <v>63</v>
+      <c r="B234" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C234" s="6">
+        <v>17</v>
       </c>
       <c r="D234" t="s">
-        <v>269</v>
+        <v>140</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>157</v>
       </c>
-      <c r="B235" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C235" s="8">
-        <v>75</v>
+      <c r="B235" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C235" s="6">
+        <v>450</v>
       </c>
       <c r="D235" t="s">
-        <v>269</v>
+        <v>143</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>157</v>
       </c>
-      <c r="B236" s="4" t="s">
-        <v>164</v>
+      <c r="B236" s="4">
+        <v>6102</v>
       </c>
       <c r="C236" s="8">
-        <v>38</v>
+        <v>23.86</v>
       </c>
       <c r="D236" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>157</v>
       </c>
-      <c r="B237" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C237" s="6">
-        <v>24</v>
+      <c r="B237" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C237" s="8">
+        <v>35.5</v>
       </c>
       <c r="D237" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>157</v>
       </c>
-      <c r="B238" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C238" s="6">
-        <v>48</v>
+      <c r="B238" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C238" s="8">
+        <v>32</v>
       </c>
       <c r="D238" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>157</v>
       </c>
-      <c r="B239" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C239" s="6">
-        <v>92</v>
+      <c r="B239" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C239" s="8">
+        <v>47</v>
       </c>
       <c r="D239" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>157</v>
       </c>
-      <c r="B240" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C240" s="6">
-        <v>38</v>
+      <c r="B240" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C240" s="8">
+        <v>53</v>
       </c>
       <c r="D240" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>157</v>
       </c>
-      <c r="B241" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C241" s="6">
-        <v>31</v>
+      <c r="B241" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C241" s="8">
+        <v>48</v>
       </c>
       <c r="D241" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>157</v>
       </c>
-      <c r="B242" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C242" s="6">
-        <v>120</v>
+      <c r="B242" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C242" s="8">
+        <v>70</v>
       </c>
       <c r="D242" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>157</v>
       </c>
-      <c r="B243" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C243" s="6">
-        <v>25</v>
+      <c r="B243" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C243" s="8">
+        <v>43</v>
       </c>
       <c r="D243" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>157</v>
       </c>
-      <c r="B244" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C244" s="6">
-        <v>37</v>
+      <c r="B244" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C244" s="8">
+        <v>46</v>
       </c>
       <c r="D244" t="s">
-        <v>146</v>
+        <v>269</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>157</v>
       </c>
-      <c r="B245" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C245" s="6">
-        <v>60</v>
+      <c r="B245" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C245" s="8">
+        <v>48</v>
       </c>
       <c r="D245" t="s">
-        <v>172</v>
+        <v>269</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>157</v>
       </c>
-      <c r="B246" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C246" s="6">
-        <v>12.6</v>
+      <c r="B246" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C246" s="8">
+        <v>53</v>
       </c>
       <c r="D246" t="s">
-        <v>148</v>
+        <v>269</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>157</v>
       </c>
-      <c r="B247" s="3">
-        <v>4442</v>
-      </c>
-      <c r="C247" s="6">
-        <v>14.53</v>
+      <c r="B247" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C247" s="8">
+        <v>63</v>
       </c>
       <c r="D247" t="s">
-        <v>148</v>
+        <v>269</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>157</v>
       </c>
-      <c r="B248" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C248" s="6">
-        <v>20.8</v>
+      <c r="B248" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C248" s="8">
+        <v>75</v>
       </c>
       <c r="D248" t="s">
-        <v>148</v>
+        <v>269</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>157</v>
       </c>
-      <c r="B249" s="3">
-        <v>4660</v>
-      </c>
-      <c r="C249" s="6">
-        <v>27</v>
+      <c r="B249" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C249" s="8">
+        <v>38</v>
       </c>
       <c r="D249" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>157</v>
       </c>
-      <c r="B250" s="3">
-        <v>6642</v>
+      <c r="B250" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="C250" s="6">
-        <v>18.52</v>
+        <v>24</v>
       </c>
       <c r="D250" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -4969,24 +5093,27 @@
         <v>157</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>99</v>
+        <v>57</v>
+      </c>
+      <c r="C251" s="6">
+        <v>48</v>
       </c>
       <c r="D251" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>157</v>
       </c>
-      <c r="B252" s="3">
-        <v>6660</v>
+      <c r="B252" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C252" s="6">
-        <v>27.05</v>
+        <v>92</v>
       </c>
       <c r="D252" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -4994,27 +5121,27 @@
         <v>157</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>100</v>
+        <v>255</v>
       </c>
       <c r="C253" s="6">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="D253" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>157</v>
       </c>
-      <c r="B254" s="3">
-        <v>8860</v>
+      <c r="B254" s="3" t="s">
+        <v>256</v>
       </c>
       <c r="C254" s="6">
-        <v>63.9</v>
+        <v>31</v>
       </c>
       <c r="D254" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -5022,13 +5149,13 @@
         <v>157</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>104</v>
+        <v>257</v>
       </c>
       <c r="C255" s="6">
-        <v>41.5</v>
+        <v>120</v>
       </c>
       <c r="D255" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -5036,13 +5163,13 @@
         <v>157</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C256" s="6">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D256" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -5050,13 +5177,13 @@
         <v>157</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>278</v>
+        <v>59</v>
       </c>
       <c r="C257" s="6">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D257" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -5064,83 +5191,83 @@
         <v>157</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>279</v>
+        <v>93</v>
       </c>
       <c r="C258" s="6">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D258" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>157</v>
       </c>
-      <c r="B259" s="3" t="s">
-        <v>118</v>
+      <c r="B259" s="3">
+        <v>4430</v>
       </c>
       <c r="C259" s="6">
-        <v>23.15</v>
+        <v>12.6</v>
       </c>
       <c r="D259" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>157</v>
       </c>
-      <c r="B260" s="3" t="s">
-        <v>119</v>
+      <c r="B260" s="3">
+        <v>4442</v>
       </c>
       <c r="C260" s="6">
-        <v>42.65</v>
+        <v>14.53</v>
       </c>
       <c r="D260" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>157</v>
       </c>
-      <c r="B261" s="3" t="s">
-        <v>120</v>
+      <c r="B261" s="3">
+        <v>4642</v>
       </c>
       <c r="C261" s="6">
-        <v>82</v>
+        <v>20.8</v>
       </c>
       <c r="D261" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>157</v>
       </c>
-      <c r="B262" s="3" t="s">
-        <v>121</v>
+      <c r="B262" s="3">
+        <v>4660</v>
       </c>
       <c r="C262" s="6">
-        <v>33.5</v>
+        <v>27</v>
       </c>
       <c r="D262" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>157</v>
       </c>
-      <c r="B263" s="3" t="s">
-        <v>122</v>
+      <c r="B263" s="3">
+        <v>6642</v>
       </c>
       <c r="C263" s="6">
-        <v>60.9</v>
+        <v>18.52</v>
       </c>
       <c r="D263" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -5148,27 +5275,24 @@
         <v>157</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C264" s="6">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D264" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>157</v>
       </c>
-      <c r="B265" s="3" t="s">
-        <v>124</v>
+      <c r="B265" s="3">
+        <v>6660</v>
       </c>
       <c r="C265" s="6">
-        <v>16</v>
+        <v>27.05</v>
       </c>
       <c r="D265" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -5176,27 +5300,27 @@
         <v>157</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C266" s="6">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="D266" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>157</v>
       </c>
-      <c r="B267" s="3" t="s">
-        <v>126</v>
+      <c r="B267" s="3">
+        <v>8860</v>
       </c>
       <c r="C267" s="6">
-        <v>21.32</v>
+        <v>63.9</v>
       </c>
       <c r="D267" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -5204,13 +5328,13 @@
         <v>157</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>165</v>
+        <v>319</v>
       </c>
       <c r="C268" s="6">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="D268" t="s">
-        <v>174</v>
+        <v>309</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -5218,13 +5342,13 @@
         <v>157</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>166</v>
+        <v>317</v>
       </c>
       <c r="C269" s="6">
-        <v>33</v>
+        <v>22.75</v>
       </c>
       <c r="D269" t="s">
-        <v>174</v>
+        <v>309</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -5232,13 +5356,13 @@
         <v>157</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>167</v>
+        <v>318</v>
       </c>
       <c r="C270" s="6">
-        <v>27</v>
+        <v>18.25</v>
       </c>
       <c r="D270" t="s">
-        <v>174</v>
+        <v>309</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -5246,13 +5370,13 @@
         <v>157</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>168</v>
+        <v>306</v>
       </c>
       <c r="C271" s="6">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="D271" t="s">
-        <v>174</v>
+        <v>309</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -5260,13 +5384,13 @@
         <v>157</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>169</v>
+        <v>307</v>
       </c>
       <c r="C272" s="6">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="D272" t="s">
-        <v>174</v>
+        <v>309</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -5274,13 +5398,13 @@
         <v>157</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="C273" s="6">
-        <v>114</v>
+        <v>41.5</v>
       </c>
       <c r="D273" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -5288,265 +5412,265 @@
         <v>157</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>171</v>
+        <v>277</v>
       </c>
       <c r="C274" s="6">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="D274" t="s">
-        <v>174</v>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>157</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C275" s="6">
+        <v>23</v>
+      </c>
+      <c r="D275" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>157</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C276" s="6">
+        <v>78</v>
+      </c>
+      <c r="D276" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>157</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C277" s="6">
+        <v>23.15</v>
+      </c>
+      <c r="D277" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>157</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C278" s="6">
+        <v>42.65</v>
+      </c>
+      <c r="D278" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C279" s="6">
-        <v>9.6</v>
+        <v>82</v>
       </c>
       <c r="D279" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="C280" s="6">
-        <v>9.5399999999999991</v>
+        <v>33.5</v>
       </c>
       <c r="D280" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="C281" s="6">
-        <v>9.6</v>
+        <v>60.9</v>
       </c>
       <c r="D281" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="C282" s="6">
-        <v>11.5</v>
+        <v>118</v>
       </c>
       <c r="D282" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="C283" s="6">
-        <v>14.99</v>
+        <v>16</v>
       </c>
       <c r="D283" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="C284" s="6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="D284" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="C285" s="6">
-        <v>17.97</v>
+        <v>21.32</v>
       </c>
       <c r="D285" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C286" s="6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D286" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C287" s="6">
-        <v>28.5</v>
+        <v>33</v>
       </c>
       <c r="D287" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C288" s="6">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D288" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C289" s="6">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D289" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C290" s="6">
-        <v>36.5</v>
+        <v>81</v>
       </c>
       <c r="D290" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>175</v>
-      </c>
-      <c r="B291" t="s">
-        <v>244</v>
+        <v>157</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="C291" s="6">
-        <v>42.9</v>
+        <v>114</v>
       </c>
       <c r="D291" t="s">
-        <v>268</v>
+        <v>174</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>175</v>
-      </c>
-      <c r="B292" t="s">
-        <v>247</v>
+        <v>157</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="C292" s="6">
-        <v>42.9</v>
+        <v>126</v>
       </c>
       <c r="D292" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>175</v>
-      </c>
-      <c r="B293" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C293" s="6">
-        <v>98.5</v>
-      </c>
-      <c r="D293" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>175</v>
-      </c>
-      <c r="B294" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C294" s="6">
-        <v>105</v>
-      </c>
-      <c r="D294" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>175</v>
-      </c>
-      <c r="B295" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C295" s="6">
-        <v>98.5</v>
-      </c>
-      <c r="D295" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>175</v>
-      </c>
-      <c r="B296" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C296" s="6">
-        <v>105</v>
-      </c>
-      <c r="D296" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -5554,13 +5678,13 @@
         <v>175</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C297" s="6">
-        <v>142</v>
+        <v>9.6</v>
       </c>
       <c r="D297" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -5568,13 +5692,13 @@
         <v>175</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C298" s="6">
-        <v>170</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="D298" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -5582,13 +5706,13 @@
         <v>175</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C299" s="6">
-        <v>234</v>
+        <v>9.6</v>
       </c>
       <c r="D299" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -5596,13 +5720,13 @@
         <v>175</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>33</v>
+        <v>158</v>
       </c>
       <c r="C300" s="6">
-        <v>255</v>
+        <v>11.5</v>
       </c>
       <c r="D300" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -5610,13 +5734,13 @@
         <v>175</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C301" s="6">
-        <v>265</v>
+        <v>14.99</v>
       </c>
       <c r="D301" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -5624,13 +5748,13 @@
         <v>175</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C302" s="6">
-        <v>140</v>
+        <v>16.5</v>
       </c>
       <c r="D302" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -5638,13 +5762,13 @@
         <v>175</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="C303" s="6">
-        <v>130</v>
+        <v>17.97</v>
       </c>
       <c r="D303" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -5652,13 +5776,13 @@
         <v>175</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>37</v>
+        <v>159</v>
       </c>
       <c r="C304" s="6">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D304" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -5666,13 +5790,13 @@
         <v>175</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="C305" s="6">
-        <v>18</v>
+        <v>28.5</v>
       </c>
       <c r="D305" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -5680,13 +5804,13 @@
         <v>175</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="C306" s="6">
-        <v>475</v>
+        <v>30</v>
       </c>
       <c r="D306" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -5694,13 +5818,13 @@
         <v>175</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>55</v>
+        <v>162</v>
       </c>
       <c r="C307" s="6">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D307" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -5708,83 +5832,83 @@
         <v>175</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>56</v>
+        <v>163</v>
       </c>
       <c r="C308" s="6">
-        <v>21</v>
+        <v>36.5</v>
       </c>
       <c r="D308" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>175</v>
       </c>
-      <c r="B309" s="3" t="s">
-        <v>57</v>
+      <c r="B309" t="s">
+        <v>244</v>
       </c>
       <c r="C309" s="6">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="D309" t="s">
-        <v>145</v>
+        <v>268</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>175</v>
       </c>
-      <c r="B310" s="3" t="s">
-        <v>58</v>
+      <c r="B310" t="s">
+        <v>247</v>
       </c>
       <c r="C310" s="6">
-        <v>80</v>
+        <v>42.9</v>
       </c>
       <c r="D310" t="s">
-        <v>145</v>
+        <v>268</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>175</v>
       </c>
-      <c r="B311" t="s">
-        <v>255</v>
+      <c r="B311" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="C311" s="6">
-        <v>16</v>
+        <v>98.5</v>
       </c>
       <c r="D311" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>175</v>
       </c>
-      <c r="B312" t="s">
-        <v>256</v>
+      <c r="B312" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C312" s="6">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="D312" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>175</v>
       </c>
-      <c r="B313" t="s">
-        <v>257</v>
+      <c r="B313" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C313" s="6">
-        <v>102</v>
+        <v>98.5</v>
       </c>
       <c r="D313" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -5792,13 +5916,13 @@
         <v>175</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C314" s="6">
-        <v>33.5</v>
+        <v>105</v>
       </c>
       <c r="D314" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -5806,27 +5930,27 @@
         <v>175</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C315" s="6">
-        <v>15.1</v>
+        <v>142</v>
       </c>
       <c r="D315" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>175</v>
       </c>
-      <c r="B316" t="s">
-        <v>61</v>
+      <c r="B316" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C316" s="6">
-        <v>38.28</v>
+        <v>170</v>
       </c>
       <c r="D316" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -5834,13 +5958,13 @@
         <v>175</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="C317" s="6">
-        <v>22.36</v>
+        <v>234</v>
       </c>
       <c r="D317" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -5848,13 +5972,13 @@
         <v>175</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>176</v>
+        <v>33</v>
       </c>
       <c r="C318" s="6">
-        <v>23.68</v>
+        <v>255</v>
       </c>
       <c r="D318" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -5862,13 +5986,13 @@
         <v>175</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C319" s="6">
-        <v>10</v>
+        <v>265</v>
       </c>
       <c r="D319" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -5876,13 +6000,13 @@
         <v>175</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>177</v>
+        <v>35</v>
       </c>
       <c r="C320" s="6">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="D320" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
@@ -5890,13 +6014,13 @@
         <v>175</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="C321" s="6">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="D321" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -5904,13 +6028,13 @@
         <v>175</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>179</v>
+        <v>37</v>
       </c>
       <c r="C322" s="6">
-        <v>421.08</v>
+        <v>58</v>
       </c>
       <c r="D322" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -5918,10 +6042,13 @@
         <v>175</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>92</v>
+        <v>23</v>
+      </c>
+      <c r="C323" s="6">
+        <v>18</v>
       </c>
       <c r="D323" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -5929,13 +6056,13 @@
         <v>175</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="C324" s="6">
-        <v>60</v>
+        <v>475</v>
       </c>
       <c r="D324" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -5943,10 +6070,13 @@
         <v>175</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>94</v>
+        <v>55</v>
+      </c>
+      <c r="C325" s="6">
+        <v>12</v>
       </c>
       <c r="D325" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -5954,77 +6084,83 @@
         <v>175</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>95</v>
+        <v>56</v>
+      </c>
+      <c r="C326" s="6">
+        <v>21</v>
       </c>
       <c r="D326" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>175</v>
       </c>
-      <c r="B327" s="3">
-        <v>4430</v>
+      <c r="B327" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="C327" s="6">
-        <v>15.25</v>
+        <v>40</v>
       </c>
       <c r="D327" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>175</v>
       </c>
-      <c r="B328" s="3">
-        <v>4442</v>
+      <c r="B328" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C328" s="6">
-        <v>18.899999999999999</v>
+        <v>80</v>
       </c>
       <c r="D328" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>175</v>
       </c>
-      <c r="B329" s="3" t="s">
-        <v>96</v>
+      <c r="B329" t="s">
+        <v>255</v>
       </c>
       <c r="C329" s="6">
-        <v>193</v>
+        <v>16</v>
       </c>
       <c r="D329" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>175</v>
       </c>
-      <c r="B330" s="3" t="s">
-        <v>97</v>
+      <c r="B330" t="s">
+        <v>256</v>
+      </c>
+      <c r="C330" s="6">
+        <v>28</v>
       </c>
       <c r="D330" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>175</v>
       </c>
-      <c r="B331" s="3">
-        <v>4642</v>
+      <c r="B331" t="s">
+        <v>257</v>
       </c>
       <c r="C331" s="6">
-        <v>20.8</v>
+        <v>102</v>
       </c>
       <c r="D331" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -6032,38 +6168,41 @@
         <v>175</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>98</v>
+        <v>59</v>
+      </c>
+      <c r="C332" s="6">
+        <v>33.5</v>
       </c>
       <c r="D332" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>175</v>
       </c>
-      <c r="B333" s="3">
-        <v>4660</v>
+      <c r="B333" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C333" s="6">
-        <v>24.7</v>
+        <v>15.1</v>
       </c>
       <c r="D333" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>175</v>
       </c>
-      <c r="B334" s="3">
-        <v>6642</v>
+      <c r="B334" t="s">
+        <v>61</v>
       </c>
       <c r="C334" s="6">
-        <v>26.8</v>
+        <v>38.28</v>
       </c>
       <c r="D334" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -6071,27 +6210,27 @@
         <v>175</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C335" s="6">
-        <v>115</v>
+        <v>22.36</v>
       </c>
       <c r="D335" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>175</v>
       </c>
-      <c r="B336" s="3">
-        <v>6660</v>
+      <c r="B336" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="C336" s="6">
-        <v>27.05</v>
+        <v>23.68</v>
       </c>
       <c r="D336" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -6099,13 +6238,13 @@
         <v>175</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="C337" s="6">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="D337" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -6113,13 +6252,13 @@
         <v>175</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C338" s="6">
-        <v>30.5</v>
+        <v>87</v>
       </c>
       <c r="D338" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -6127,13 +6266,13 @@
         <v>175</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>271</v>
+        <v>178</v>
       </c>
       <c r="C339" s="6">
-        <v>12.75</v>
+        <v>225</v>
       </c>
       <c r="D339" t="s">
-        <v>270</v>
+        <v>147</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -6141,13 +6280,13 @@
         <v>175</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>259</v>
+        <v>179</v>
       </c>
       <c r="C340" s="6">
-        <v>12.75</v>
+        <v>421.08</v>
       </c>
       <c r="D340" t="s">
-        <v>270</v>
+        <v>147</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -6155,13 +6294,10 @@
         <v>175</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C341" s="6">
-        <v>13.25</v>
+        <v>92</v>
       </c>
       <c r="D341" t="s">
-        <v>270</v>
+        <v>148</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -6169,13 +6305,13 @@
         <v>175</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>260</v>
+        <v>93</v>
       </c>
       <c r="C342" s="6">
-        <v>10.3</v>
+        <v>60</v>
       </c>
       <c r="D342" t="s">
-        <v>270</v>
+        <v>172</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -6183,13 +6319,10 @@
         <v>175</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C343" s="6">
-        <v>11.85</v>
+        <v>94</v>
       </c>
       <c r="D343" t="s">
-        <v>270</v>
+        <v>148</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -6197,41 +6330,38 @@
         <v>175</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C344" s="6">
-        <v>12.75</v>
+        <v>95</v>
       </c>
       <c r="D344" t="s">
-        <v>270</v>
+        <v>148</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>175</v>
       </c>
-      <c r="B345" s="3" t="s">
-        <v>262</v>
+      <c r="B345" s="3">
+        <v>4430</v>
       </c>
       <c r="C345" s="6">
-        <v>10.3</v>
+        <v>15.25</v>
       </c>
       <c r="D345" t="s">
-        <v>270</v>
+        <v>148</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>175</v>
       </c>
-      <c r="B346" s="3" t="s">
-        <v>263</v>
+      <c r="B346" s="3">
+        <v>4442</v>
       </c>
       <c r="C346" s="6">
-        <v>13.25</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D346" t="s">
-        <v>270</v>
+        <v>148</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -6239,13 +6369,13 @@
         <v>175</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>272</v>
+        <v>96</v>
       </c>
       <c r="C347" s="6">
-        <v>12.75</v>
+        <v>193</v>
       </c>
       <c r="D347" t="s">
-        <v>270</v>
+        <v>148</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -6253,27 +6383,24 @@
         <v>175</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C348" s="6">
-        <v>21.5</v>
+        <v>97</v>
       </c>
       <c r="D348" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>175</v>
       </c>
-      <c r="B349" s="3" t="s">
-        <v>108</v>
+      <c r="B349" s="3">
+        <v>4642</v>
       </c>
       <c r="C349" s="6">
-        <v>22.5</v>
+        <v>20.8</v>
       </c>
       <c r="D349" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
@@ -6281,41 +6408,38 @@
         <v>175</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C350" s="6">
-        <v>10.5</v>
+        <v>98</v>
       </c>
       <c r="D350" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>175</v>
       </c>
-      <c r="B351" s="3" t="s">
-        <v>116</v>
+      <c r="B351" s="3">
+        <v>4660</v>
       </c>
       <c r="C351" s="6">
-        <v>10.5</v>
+        <v>24.7</v>
       </c>
       <c r="D351" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>175</v>
       </c>
-      <c r="B352" s="3" t="s">
-        <v>117</v>
+      <c r="B352" s="3">
+        <v>6642</v>
       </c>
       <c r="C352" s="6">
-        <v>10.5</v>
+        <v>26.8</v>
       </c>
       <c r="D352" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -6323,24 +6447,27 @@
         <v>175</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>277</v>
+        <v>99</v>
+      </c>
+      <c r="C353" s="6">
+        <v>115</v>
       </c>
       <c r="D353" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>175</v>
       </c>
-      <c r="B354" s="3" t="s">
-        <v>278</v>
+      <c r="B354" s="3">
+        <v>6660</v>
       </c>
       <c r="C354" s="6">
-        <v>23</v>
+        <v>27.05</v>
       </c>
       <c r="D354" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -6348,10 +6475,13 @@
         <v>175</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>279</v>
+        <v>100</v>
+      </c>
+      <c r="C355" s="6">
+        <v>160</v>
       </c>
       <c r="D355" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -6359,13 +6489,13 @@
         <v>175</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="C356" s="6">
-        <v>23.15</v>
+        <v>30.5</v>
       </c>
       <c r="D356" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -6373,13 +6503,13 @@
         <v>175</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>119</v>
+        <v>271</v>
       </c>
       <c r="C357" s="6">
-        <v>42.65</v>
+        <v>12.75</v>
       </c>
       <c r="D357" t="s">
-        <v>153</v>
+        <v>270</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -6387,13 +6517,13 @@
         <v>175</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>120</v>
+        <v>259</v>
       </c>
       <c r="C358" s="6">
-        <v>82</v>
+        <v>12.75</v>
       </c>
       <c r="D358" t="s">
-        <v>153</v>
+        <v>270</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -6401,13 +6531,13 @@
         <v>175</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>121</v>
+        <v>261</v>
       </c>
       <c r="C359" s="6">
-        <v>33.5</v>
+        <v>13.25</v>
       </c>
       <c r="D359" t="s">
-        <v>153</v>
+        <v>270</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -6415,13 +6545,13 @@
         <v>175</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>122</v>
+        <v>260</v>
       </c>
       <c r="C360" s="6">
-        <v>60.9</v>
+        <v>10.3</v>
       </c>
       <c r="D360" t="s">
-        <v>153</v>
+        <v>270</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -6429,13 +6559,13 @@
         <v>175</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>123</v>
+        <v>258</v>
       </c>
       <c r="C361" s="6">
-        <v>118</v>
+        <v>11.85</v>
       </c>
       <c r="D361" t="s">
-        <v>153</v>
+        <v>270</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -6443,13 +6573,13 @@
         <v>175</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="C362" s="6">
-        <v>16</v>
+        <v>12.75</v>
       </c>
       <c r="D362" t="s">
-        <v>153</v>
+        <v>270</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
@@ -6457,13 +6587,13 @@
         <v>175</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>125</v>
+        <v>262</v>
       </c>
       <c r="C363" s="6">
-        <v>16</v>
+        <v>10.3</v>
       </c>
       <c r="D363" t="s">
-        <v>153</v>
+        <v>270</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -6471,13 +6601,13 @@
         <v>175</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>126</v>
+        <v>263</v>
       </c>
       <c r="C364" s="6">
-        <v>21.32</v>
+        <v>13.25</v>
       </c>
       <c r="D364" t="s">
-        <v>153</v>
+        <v>270</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -6485,13 +6615,13 @@
         <v>175</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>127</v>
+        <v>272</v>
       </c>
       <c r="C365" s="6">
-        <v>26</v>
+        <v>12.75</v>
       </c>
       <c r="D365" t="s">
-        <v>154</v>
+        <v>270</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -6499,10 +6629,13 @@
         <v>175</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>128</v>
+        <v>107</v>
+      </c>
+      <c r="C366" s="6">
+        <v>21.5</v>
       </c>
       <c r="D366" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -6510,13 +6643,13 @@
         <v>175</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="C367" s="6">
-        <v>13.42</v>
+        <v>22.5</v>
       </c>
       <c r="D367" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -6524,10 +6657,13 @@
         <v>175</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>130</v>
+        <v>115</v>
+      </c>
+      <c r="C368" s="6">
+        <v>10.5</v>
       </c>
       <c r="D368" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -6535,10 +6671,13 @@
         <v>175</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>131</v>
+        <v>116</v>
+      </c>
+      <c r="C369" s="6">
+        <v>10.5</v>
       </c>
       <c r="D369" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -6546,251 +6685,250 @@
         <v>175</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C370" s="6">
-        <v>9.5399999999999991</v>
+        <v>10.5</v>
       </c>
       <c r="D370" t="s">
-        <v>154</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>175</v>
+      </c>
+      <c r="B371" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D371" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>175</v>
+      </c>
+      <c r="B372" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C372" s="6">
+        <v>23</v>
+      </c>
+      <c r="D372" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>175</v>
+      </c>
+      <c r="B373" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D373" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="C374" s="6">
-        <v>24.99</v>
+        <v>23.15</v>
       </c>
       <c r="D374" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="C375" s="6">
-        <v>34.99</v>
+        <v>42.65</v>
       </c>
       <c r="D375" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="C376" s="6">
-        <v>19.989999999999998</v>
+        <v>82</v>
       </c>
       <c r="D376" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="C377" s="6">
-        <v>29.99</v>
+        <v>33.5</v>
       </c>
       <c r="D377" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="C378" s="6">
-        <v>189.99</v>
+        <v>60.9</v>
       </c>
       <c r="D378" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="C379" s="6">
-        <v>229.99</v>
+        <v>118</v>
       </c>
       <c r="D379" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="C380" s="6">
-        <v>299.99</v>
+        <v>16</v>
       </c>
       <c r="D380" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="C381" s="6">
-        <v>189.99</v>
+        <v>16</v>
       </c>
       <c r="D381" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="C382" s="6">
-        <v>229</v>
+        <v>21.32</v>
       </c>
       <c r="D382" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="C383" s="6">
-        <v>299.99</v>
+        <v>26</v>
       </c>
       <c r="D383" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C384" s="6">
-        <v>309</v>
+        <v>128</v>
       </c>
       <c r="D384" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="C385" s="6">
-        <v>345</v>
+        <v>13.42</v>
       </c>
       <c r="D385" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C386" s="6">
-        <v>409</v>
+        <v>130</v>
       </c>
       <c r="D386" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C387" s="6">
-        <v>389</v>
+        <v>131</v>
       </c>
       <c r="D387" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>184</v>
+        <v>132</v>
       </c>
       <c r="C388" s="6">
-        <v>389.99</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="D388" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A389" t="s">
-        <v>181</v>
-      </c>
-      <c r="B389" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C389" s="6">
-        <v>399.99</v>
-      </c>
-      <c r="D389" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A390" t="s">
-        <v>181</v>
-      </c>
-      <c r="B390" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C390" s="6">
-        <v>399.99</v>
-      </c>
-      <c r="D390" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -6798,13 +6936,13 @@
         <v>181</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>37</v>
+        <v>320</v>
       </c>
       <c r="C391" s="6">
-        <v>89.23</v>
+        <v>14.5</v>
       </c>
       <c r="D391" t="s">
-        <v>142</v>
+        <v>320</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -6812,10 +6950,13 @@
         <v>181</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>36</v>
+        <v>6</v>
+      </c>
+      <c r="C392" s="6">
+        <v>24.99</v>
       </c>
       <c r="D392" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -6823,13 +6964,13 @@
         <v>181</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C393" s="6">
-        <v>219.99</v>
+        <v>34.99</v>
       </c>
       <c r="D393" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -6837,13 +6978,13 @@
         <v>181</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="C394" s="6">
-        <v>429</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D394" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -6851,13 +6992,13 @@
         <v>181</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="C395" s="6">
-        <v>439</v>
+        <v>29.99</v>
       </c>
       <c r="D395" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -6865,10 +7006,10 @@
         <v>181</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>188</v>
+        <v>28</v>
       </c>
       <c r="C396" s="6">
-        <v>199</v>
+        <v>189.99</v>
       </c>
       <c r="D396" t="s">
         <v>142</v>
@@ -6879,10 +7020,10 @@
         <v>181</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="C397" s="6">
-        <v>249</v>
+        <v>229.99</v>
       </c>
       <c r="D397" t="s">
         <v>142</v>
@@ -6893,10 +7034,10 @@
         <v>181</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C398" s="6">
-        <v>670</v>
+        <v>299.99</v>
       </c>
       <c r="D398" t="s">
         <v>142</v>
@@ -6907,10 +7048,10 @@
         <v>181</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>191</v>
+        <v>26</v>
       </c>
       <c r="C399" s="6">
-        <v>49.99</v>
+        <v>189.99</v>
       </c>
       <c r="D399" t="s">
         <v>142</v>
@@ -6921,10 +7062,10 @@
         <v>181</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="C400" s="6">
-        <v>49.99</v>
+        <v>229</v>
       </c>
       <c r="D400" t="s">
         <v>142</v>
@@ -6935,13 +7076,13 @@
         <v>181</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C401" s="6">
-        <v>11.49</v>
+        <v>299.99</v>
       </c>
       <c r="D401" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
@@ -6949,13 +7090,13 @@
         <v>181</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>194</v>
+        <v>30</v>
       </c>
       <c r="C402" s="6">
-        <v>18.95</v>
+        <v>309</v>
       </c>
       <c r="D402" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -6963,27 +7104,27 @@
         <v>181</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="C403" s="6">
-        <v>39.99</v>
+        <v>345</v>
       </c>
       <c r="D403" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>181</v>
       </c>
-      <c r="B404" s="3">
-        <v>6102</v>
+      <c r="B404" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C404" s="6">
-        <v>44.5</v>
+        <v>409</v>
       </c>
       <c r="D404" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
@@ -6991,13 +7132,13 @@
         <v>181</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>196</v>
+        <v>33</v>
       </c>
       <c r="C405" s="6">
-        <v>112</v>
+        <v>389</v>
       </c>
       <c r="D405" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
@@ -7005,13 +7146,13 @@
         <v>181</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C406" s="6">
-        <v>139</v>
+        <v>389.99</v>
       </c>
       <c r="D406" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
@@ -7019,13 +7160,13 @@
         <v>181</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="C407" s="6">
-        <v>139</v>
+        <v>399.99</v>
       </c>
       <c r="D407" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
@@ -7033,10 +7174,13 @@
         <v>181</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
+      </c>
+      <c r="C408" s="6">
+        <v>399.99</v>
       </c>
       <c r="D408" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
@@ -7044,10 +7188,13 @@
         <v>181</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>200</v>
+        <v>37</v>
+      </c>
+      <c r="C409" s="6">
+        <v>89.23</v>
       </c>
       <c r="D409" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
@@ -7055,13 +7202,10 @@
         <v>181</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C410" s="6">
-        <v>209</v>
+        <v>36</v>
       </c>
       <c r="D410" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
@@ -7069,10 +7213,13 @@
         <v>181</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>202</v>
+        <v>35</v>
+      </c>
+      <c r="C411" s="6">
+        <v>219.99</v>
       </c>
       <c r="D411" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
@@ -7080,10 +7227,13 @@
         <v>181</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>203</v>
+        <v>186</v>
+      </c>
+      <c r="C412" s="6">
+        <v>429</v>
       </c>
       <c r="D412" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
@@ -7091,13 +7241,13 @@
         <v>181</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="C413" s="6">
-        <v>179</v>
+        <v>439</v>
       </c>
       <c r="D413" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
@@ -7105,13 +7255,13 @@
         <v>181</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="C414" s="6">
-        <v>299.99</v>
+        <v>199</v>
       </c>
       <c r="D414" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
@@ -7119,13 +7269,13 @@
         <v>181</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="C415" s="6">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="D415" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
@@ -7133,13 +7283,13 @@
         <v>181</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="C416" s="6">
-        <v>245</v>
+        <v>670</v>
       </c>
       <c r="D416" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
@@ -7147,13 +7297,13 @@
         <v>181</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="C417" s="6">
-        <v>240</v>
+        <v>49.99</v>
       </c>
       <c r="D417" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
@@ -7161,13 +7311,13 @@
         <v>181</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="C418" s="6">
-        <v>399</v>
+        <v>49.99</v>
       </c>
       <c r="D418" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
@@ -7175,10 +7325,10 @@
         <v>181</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="C419" s="6">
-        <v>209</v>
+        <v>11.49</v>
       </c>
       <c r="D419" t="s">
         <v>144</v>
@@ -7189,10 +7339,10 @@
         <v>181</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="C420" s="6">
-        <v>345</v>
+        <v>18.95</v>
       </c>
       <c r="D420" t="s">
         <v>144</v>
@@ -7203,10 +7353,10 @@
         <v>181</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="C421" s="6">
-        <v>209</v>
+        <v>39.99</v>
       </c>
       <c r="D421" t="s">
         <v>144</v>
@@ -7216,11 +7366,11 @@
       <c r="A422" t="s">
         <v>181</v>
       </c>
-      <c r="B422" s="3" t="s">
-        <v>213</v>
+      <c r="B422" s="3">
+        <v>6102</v>
       </c>
       <c r="C422" s="6">
-        <v>369</v>
+        <v>44.5</v>
       </c>
       <c r="D422" t="s">
         <v>144</v>
@@ -7231,10 +7381,10 @@
         <v>181</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="C423" s="6">
-        <v>315</v>
+        <v>112</v>
       </c>
       <c r="D423" t="s">
         <v>144</v>
@@ -7245,10 +7395,10 @@
         <v>181</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="C424" s="6">
-        <v>265</v>
+        <v>139</v>
       </c>
       <c r="D424" t="s">
         <v>144</v>
@@ -7259,10 +7409,10 @@
         <v>181</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="C425" s="6">
-        <v>251</v>
+        <v>139</v>
       </c>
       <c r="D425" t="s">
         <v>144</v>
@@ -7273,10 +7423,7 @@
         <v>181</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C426" s="6">
-        <v>420</v>
+        <v>199</v>
       </c>
       <c r="D426" t="s">
         <v>144</v>
@@ -7287,10 +7434,7 @@
         <v>181</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C427" s="6">
-        <v>315</v>
+        <v>200</v>
       </c>
       <c r="D427" t="s">
         <v>144</v>
@@ -7301,10 +7445,10 @@
         <v>181</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C428" s="6">
-        <v>365</v>
+        <v>209</v>
       </c>
       <c r="D428" t="s">
         <v>144</v>
@@ -7315,10 +7459,7 @@
         <v>181</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C429" s="6">
-        <v>285</v>
+        <v>202</v>
       </c>
       <c r="D429" t="s">
         <v>144</v>
@@ -7329,13 +7470,10 @@
         <v>181</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C430" s="6">
-        <v>55.99</v>
+        <v>203</v>
       </c>
       <c r="D430" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
@@ -7343,13 +7481,13 @@
         <v>181</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="C431" s="6">
-        <v>39.99</v>
+        <v>179</v>
       </c>
       <c r="D431" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
@@ -7357,13 +7495,13 @@
         <v>181</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>57</v>
+        <v>205</v>
       </c>
       <c r="C432" s="6">
-        <v>68</v>
+        <v>299.99</v>
       </c>
       <c r="D432" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
@@ -7371,13 +7509,13 @@
         <v>181</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>58</v>
+        <v>206</v>
       </c>
       <c r="C433" s="6">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="D433" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
@@ -7385,13 +7523,13 @@
         <v>181</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>255</v>
+        <v>207</v>
       </c>
       <c r="C434" s="6">
-        <v>30.99</v>
+        <v>245</v>
       </c>
       <c r="D434" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
@@ -7399,13 +7537,13 @@
         <v>181</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="C435" s="6">
-        <v>42.99</v>
+        <v>240</v>
       </c>
       <c r="D435" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
@@ -7413,13 +7551,13 @@
         <v>181</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>257</v>
+        <v>209</v>
       </c>
       <c r="C436" s="6">
-        <v>159</v>
+        <v>399</v>
       </c>
       <c r="D436" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
@@ -7427,13 +7565,13 @@
         <v>181</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>274</v>
+        <v>210</v>
       </c>
       <c r="C437" s="6">
-        <v>49.99</v>
+        <v>209</v>
       </c>
       <c r="D437" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
@@ -7441,13 +7579,13 @@
         <v>181</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="C438" s="6">
-        <v>129</v>
+        <v>345</v>
       </c>
       <c r="D438" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
@@ -7455,13 +7593,13 @@
         <v>181</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="C439" s="6">
-        <v>47.99</v>
+        <v>209</v>
       </c>
       <c r="D439" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
@@ -7469,13 +7607,13 @@
         <v>181</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C440" s="6">
-        <v>34.99</v>
+        <v>369</v>
       </c>
       <c r="D440" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
@@ -7483,13 +7621,13 @@
         <v>181</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="C441" s="6">
-        <v>89.99</v>
+        <v>315</v>
       </c>
       <c r="D441" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
@@ -7497,13 +7635,13 @@
         <v>181</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="C442" s="6">
-        <v>45</v>
+        <v>265</v>
       </c>
       <c r="D442" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
@@ -7511,13 +7649,13 @@
         <v>181</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C443" s="6">
-        <v>88</v>
+        <v>251</v>
       </c>
       <c r="D443" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
@@ -7525,13 +7663,13 @@
         <v>181</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C444" s="6">
-        <v>125</v>
+        <v>420</v>
       </c>
       <c r="D444" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
@@ -7539,13 +7677,13 @@
         <v>181</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>105</v>
+        <v>218</v>
       </c>
       <c r="C445" s="6">
-        <v>79.989999999999995</v>
+        <v>315</v>
       </c>
       <c r="D445" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
@@ -7553,13 +7691,13 @@
         <v>181</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>280</v>
+        <v>219</v>
       </c>
       <c r="C446" s="6">
-        <v>7.95</v>
+        <v>365</v>
       </c>
       <c r="D446" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
@@ -7567,13 +7705,13 @@
         <v>181</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>277</v>
+        <v>220</v>
       </c>
       <c r="C447" s="6">
-        <v>18.95</v>
+        <v>285</v>
       </c>
       <c r="D447" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
@@ -7581,13 +7719,13 @@
         <v>181</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>278</v>
+        <v>54</v>
       </c>
       <c r="C448" s="6">
-        <v>36.950000000000003</v>
+        <v>55.99</v>
       </c>
       <c r="D448" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
@@ -7595,304 +7733,402 @@
         <v>181</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="C449" s="6">
         <v>39.99</v>
       </c>
       <c r="D449" t="s">
-        <v>154</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>181</v>
+      </c>
+      <c r="B450" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C450" s="6">
+        <v>68</v>
+      </c>
+      <c r="D450" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>181</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C451" s="6">
+        <v>129</v>
+      </c>
+      <c r="D451" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>181</v>
+      </c>
+      <c r="B452" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C452" s="6">
+        <v>30.99</v>
+      </c>
+      <c r="D452" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="C453" s="6">
-        <v>42.75</v>
+        <v>42.99</v>
       </c>
       <c r="D453" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="C454" s="6">
-        <v>79.47</v>
+        <v>159</v>
       </c>
       <c r="D454" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="C455" s="6">
-        <v>92.85</v>
+        <v>49.99</v>
       </c>
       <c r="D455" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>224</v>
-      </c>
-      <c r="B456" s="3">
-        <v>4430</v>
+        <v>181</v>
+      </c>
+      <c r="B456" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="C456" s="6">
-        <v>15.25</v>
+        <v>129</v>
       </c>
       <c r="D456" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>224</v>
-      </c>
-      <c r="B457" s="3">
-        <v>4442</v>
+        <v>181</v>
+      </c>
+      <c r="B457" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="C457" s="6">
-        <v>18.899999999999999</v>
+        <v>47.99</v>
       </c>
       <c r="D457" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>224</v>
-      </c>
-      <c r="B458" s="3">
-        <v>6642</v>
+        <v>181</v>
+      </c>
+      <c r="B458" s="3" t="s">
+        <v>221</v>
       </c>
       <c r="C458" s="6">
-        <v>26.8</v>
+        <v>34.99</v>
       </c>
       <c r="D458" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>224</v>
-      </c>
-      <c r="B459" s="3">
-        <v>6660</v>
+        <v>181</v>
+      </c>
+      <c r="B459" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="C459" s="6">
-        <v>27.05</v>
+        <v>89.99</v>
       </c>
       <c r="D459" t="s">
-        <v>148</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>181</v>
+      </c>
+      <c r="B460" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C460" s="6">
+        <v>45</v>
+      </c>
+      <c r="D460" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>181</v>
+      </c>
+      <c r="B461" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C461" s="6">
+        <v>88</v>
+      </c>
+      <c r="D461" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>9</v>
+        <v>223</v>
       </c>
       <c r="C462" s="6">
-        <v>47.95</v>
+        <v>125</v>
       </c>
       <c r="D462" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="C463" s="6">
-        <v>59.07</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D463" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>11</v>
+        <v>280</v>
       </c>
       <c r="C464" s="6">
-        <v>83.8</v>
+        <v>7.95</v>
       </c>
       <c r="D464" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>12</v>
+        <v>277</v>
       </c>
       <c r="C465" s="6">
-        <v>115.4</v>
+        <v>18.95</v>
       </c>
       <c r="D465" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>13</v>
+        <v>278</v>
       </c>
       <c r="C466" s="6">
-        <v>107.15</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="D466" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="C467" s="6">
-        <v>13</v>
+        <v>39.99</v>
       </c>
       <c r="D467" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C468" s="6">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="D468" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>59</v>
+        <v>321</v>
       </c>
       <c r="C469" s="6">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="D469" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>228</v>
-      </c>
-      <c r="B470" s="3">
-        <v>4430</v>
+        <v>181</v>
+      </c>
+      <c r="B470" s="3" t="s">
+        <v>322</v>
       </c>
       <c r="C470" s="6">
-        <v>15.25</v>
+        <v>98.45</v>
       </c>
       <c r="D470" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>228</v>
-      </c>
-      <c r="B471" s="3">
-        <v>4442</v>
+        <v>181</v>
+      </c>
+      <c r="B471" s="3" t="s">
+        <v>323</v>
       </c>
       <c r="C471" s="6">
-        <v>18.899999999999999</v>
+        <v>139</v>
       </c>
       <c r="D471" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>228</v>
-      </c>
-      <c r="B472" s="3">
-        <v>6642</v>
+        <v>181</v>
+      </c>
+      <c r="B472" s="3" t="s">
+        <v>324</v>
       </c>
       <c r="C472" s="6">
-        <v>26.8</v>
+        <v>199</v>
       </c>
       <c r="D472" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>104</v>
+        <v>325</v>
       </c>
       <c r="C473" s="6">
-        <v>39.950000000000003</v>
+        <v>169.99</v>
       </c>
       <c r="D473" t="s">
-        <v>150</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>181</v>
+      </c>
+      <c r="B474" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C474" s="6">
+        <v>239.08</v>
+      </c>
+      <c r="D474" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>181</v>
+      </c>
+      <c r="B475" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C475" s="6">
+        <v>219</v>
+      </c>
+      <c r="D475" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>230</v>
+        <v>328</v>
       </c>
       <c r="C476" s="6">
-        <v>9.92</v>
+        <v>189.99</v>
       </c>
       <c r="D476" t="s">
-        <v>231</v>
+        <v>139</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>9</v>
+        <v>329</v>
       </c>
       <c r="C477" s="6">
-        <v>47.95</v>
+        <v>248</v>
       </c>
       <c r="D477" t="s">
         <v>139</v>
@@ -7900,13 +8136,13 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>10</v>
+        <v>330</v>
       </c>
       <c r="C478" s="6">
-        <v>55.73</v>
+        <v>297</v>
       </c>
       <c r="D478" t="s">
         <v>139</v>
@@ -7914,144 +8150,27 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>11</v>
+        <v>331</v>
       </c>
       <c r="C479" s="6">
-        <v>79.06</v>
+        <v>322</v>
       </c>
       <c r="D479" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A480" t="s">
-        <v>229</v>
-      </c>
-      <c r="B480" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C480" s="6">
-        <v>108.86</v>
-      </c>
-      <c r="D480" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A481" t="s">
-        <v>229</v>
-      </c>
-      <c r="B481" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C481" s="6">
-        <v>101.09</v>
-      </c>
-      <c r="D481" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A482" t="s">
-        <v>229</v>
-      </c>
-      <c r="B482" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C482" s="6">
-        <v>160.69999999999999</v>
-      </c>
-      <c r="D482" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A483" t="s">
-        <v>229</v>
-      </c>
-      <c r="B483" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C483" s="6">
-        <v>121.82</v>
-      </c>
-      <c r="D483" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A484" t="s">
-        <v>229</v>
-      </c>
-      <c r="B484" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C484" s="6">
-        <v>122.49</v>
-      </c>
-      <c r="D484" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A485" t="s">
-        <v>229</v>
-      </c>
-      <c r="B485" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D485" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A486" t="s">
-        <v>229</v>
-      </c>
-      <c r="B486" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D486" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A487" t="s">
-        <v>229</v>
-      </c>
-      <c r="B487" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D487" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A488" t="s">
-        <v>229</v>
-      </c>
-      <c r="B488" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C488" s="6">
-        <v>44</v>
-      </c>
-      <c r="D488" t="s">
-        <v>139</v>
-      </c>
-    </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C489" s="6">
-        <v>67</v>
+        <v>42.75</v>
       </c>
       <c r="D489" t="s">
         <v>139</v>
@@ -8059,13 +8178,13 @@
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B490" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C490" s="6">
-        <v>79</v>
+        <v>79.47</v>
       </c>
       <c r="D490" t="s">
         <v>139</v>
@@ -8073,35 +8192,41 @@
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>92</v>
+        <v>227</v>
+      </c>
+      <c r="C491" s="6">
+        <v>92.85</v>
       </c>
       <c r="D491" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B492" s="3">
         <v>4430</v>
       </c>
+      <c r="C492" s="6">
+        <v>15.25</v>
+      </c>
       <c r="D492" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B493" s="3">
         <v>4442</v>
       </c>
       <c r="C493" s="6">
-        <v>15</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D493" t="s">
         <v>148</v>
@@ -8109,13 +8234,13 @@
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>229</v>
-      </c>
-      <c r="B494" s="3" t="s">
-        <v>96</v>
+        <v>224</v>
+      </c>
+      <c r="B494" s="3">
+        <v>6642</v>
       </c>
       <c r="C494" s="6">
-        <v>171</v>
+        <v>26.8</v>
       </c>
       <c r="D494" t="s">
         <v>148</v>
@@ -8123,141 +8248,153 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>229</v>
-      </c>
-      <c r="B495" s="3" t="s">
-        <v>97</v>
+        <v>224</v>
+      </c>
+      <c r="B495" s="3">
+        <v>6660</v>
+      </c>
+      <c r="C495" s="6">
+        <v>27.05</v>
       </c>
       <c r="D495" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A496" t="s">
-        <v>229</v>
-      </c>
-      <c r="B496" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C496" s="6">
-        <v>16.5</v>
-      </c>
-      <c r="D496" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A497" t="s">
-        <v>229</v>
-      </c>
-      <c r="B497" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C497" s="6">
-        <v>126</v>
-      </c>
-      <c r="D497" t="s">
-        <v>148</v>
-      </c>
-    </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>229</v>
-      </c>
-      <c r="B498" s="3">
-        <v>4660</v>
+        <v>228</v>
+      </c>
+      <c r="B498" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C498" s="6">
-        <v>20.25</v>
+        <v>47.95</v>
       </c>
       <c r="D498" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>229</v>
-      </c>
-      <c r="B499" s="3">
-        <v>6630</v>
+        <v>228</v>
+      </c>
+      <c r="B499" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C499" s="6">
+        <v>59.07</v>
       </c>
       <c r="D499" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>229</v>
-      </c>
-      <c r="B500" s="3">
-        <v>6642</v>
+        <v>228</v>
+      </c>
+      <c r="B500" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C500" s="6">
-        <v>18.5</v>
+        <v>83.8</v>
       </c>
       <c r="D500" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="C501" s="6">
-        <v>103.5</v>
+        <v>115.4</v>
       </c>
       <c r="D501" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>229</v>
-      </c>
-      <c r="B502" s="3">
-        <v>6660</v>
+        <v>228</v>
+      </c>
+      <c r="B502" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C502" s="6">
-        <v>22.5</v>
+        <v>107.15</v>
       </c>
       <c r="D502" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C503" s="6">
-        <v>126</v>
+        <v>13</v>
       </c>
       <c r="D503" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>229</v>
-      </c>
-      <c r="B504" s="3">
-        <v>8860</v>
+        <v>228</v>
+      </c>
+      <c r="B504" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C504" s="6">
+        <v>17</v>
       </c>
       <c r="D504" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>228</v>
+      </c>
+      <c r="B505" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C505" s="6">
+        <v>30</v>
+      </c>
+      <c r="D505" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>228</v>
+      </c>
+      <c r="B506" s="3">
+        <v>4430</v>
+      </c>
+      <c r="C506" s="6">
+        <v>15.25</v>
+      </c>
+      <c r="D506" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>232</v>
-      </c>
-      <c r="B507" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
+      </c>
+      <c r="B507" s="3">
+        <v>4442</v>
+      </c>
+      <c r="C507" s="6">
+        <v>18.899999999999999</v>
       </c>
       <c r="D507" t="s">
         <v>148</v>
@@ -8265,13 +8402,13 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B508" s="3">
-        <v>4430</v>
+        <v>6642</v>
       </c>
       <c r="C508" s="6">
-        <v>15.25</v>
+        <v>26.8</v>
       </c>
       <c r="D508" t="s">
         <v>148</v>
@@ -8279,181 +8416,186 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>232</v>
-      </c>
-      <c r="B509" s="3">
-        <v>4442</v>
+        <v>228</v>
+      </c>
+      <c r="B509" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="C509" s="6">
-        <v>15</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="D509" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A510" t="s">
-        <v>232</v>
-      </c>
-      <c r="B510" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C510" s="6">
-        <v>171</v>
-      </c>
-      <c r="D510" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A511" t="s">
-        <v>232</v>
-      </c>
-      <c r="B511" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C511" s="6">
-        <v>972</v>
-      </c>
-      <c r="D511" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>232</v>
-      </c>
-      <c r="B512" s="3">
-        <v>4642</v>
+        <v>229</v>
+      </c>
+      <c r="B512" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="C512" s="6">
-        <v>16.5</v>
+        <v>9.92</v>
       </c>
       <c r="D512" t="s">
-        <v>148</v>
+        <v>231</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="C513" s="6">
-        <v>126</v>
+        <v>47.95</v>
       </c>
       <c r="D513" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>232</v>
-      </c>
-      <c r="B514" s="3">
-        <v>4660</v>
+        <v>229</v>
+      </c>
+      <c r="B514" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C514" s="6">
-        <v>20.25</v>
+        <v>55.73</v>
       </c>
       <c r="D514" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>232</v>
-      </c>
-      <c r="B515" s="3">
-        <v>6630</v>
+        <v>229</v>
+      </c>
+      <c r="B515" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C515" s="6">
-        <v>19</v>
+        <v>79.06</v>
       </c>
       <c r="D515" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>232</v>
-      </c>
-      <c r="B516" s="3">
-        <v>6642</v>
+        <v>229</v>
+      </c>
+      <c r="B516" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="C516" s="6">
-        <v>18.5</v>
+        <v>108.86</v>
       </c>
       <c r="D516" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="C517" s="6">
-        <v>103.5</v>
+        <v>101.09</v>
       </c>
       <c r="D517" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>232</v>
-      </c>
-      <c r="B518" s="3">
-        <v>6660</v>
+        <v>229</v>
+      </c>
+      <c r="B518" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C518" s="6">
-        <v>22.5</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="D518" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="C519" s="6">
-        <v>126</v>
+        <v>121.82</v>
       </c>
       <c r="D519" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>232</v>
-      </c>
-      <c r="B520" s="3">
-        <v>8860</v>
+        <v>229</v>
+      </c>
+      <c r="B520" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="C520" s="6">
-        <v>42.25</v>
+        <v>122.49</v>
       </c>
       <c r="D520" t="s">
-        <v>148</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>229</v>
+      </c>
+      <c r="B521" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D521" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>229</v>
+      </c>
+      <c r="B522" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D522" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>229</v>
+      </c>
+      <c r="B523" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D523" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>276</v>
+        <v>229</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C524" s="6">
-        <v>50.35</v>
+        <v>44</v>
       </c>
       <c r="D524" t="s">
         <v>139</v>
@@ -8461,752 +8603,695 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>276</v>
+        <v>229</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>104</v>
+        <v>226</v>
       </c>
       <c r="C525" s="6">
-        <v>41.99</v>
+        <v>67</v>
       </c>
       <c r="D525" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>276</v>
+        <v>229</v>
       </c>
       <c r="B526" s="3" t="s">
-        <v>58</v>
+        <v>227</v>
       </c>
       <c r="C526" s="6">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D526" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>276</v>
+        <v>229</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C527" s="6">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="D527" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>276</v>
-      </c>
-      <c r="B528" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C528" s="6">
-        <v>28.05</v>
+        <v>229</v>
+      </c>
+      <c r="B528" s="3">
+        <v>4430</v>
       </c>
       <c r="D528" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>276</v>
-      </c>
-      <c r="B529" s="3" t="s">
-        <v>113</v>
+        <v>229</v>
+      </c>
+      <c r="B529" s="3">
+        <v>4442</v>
       </c>
       <c r="C529" s="6">
-        <v>28.05</v>
+        <v>15</v>
       </c>
       <c r="D529" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>276</v>
+        <v>229</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C530" s="6">
-        <v>28.05</v>
+        <v>171</v>
       </c>
       <c r="D530" t="s">
-        <v>152</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>229</v>
+      </c>
+      <c r="B531" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D531" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>229</v>
+      </c>
+      <c r="B532" s="3">
+        <v>4642</v>
+      </c>
+      <c r="C532" s="6">
+        <v>16.5</v>
+      </c>
+      <c r="D532" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>144</v>
+        <v>229</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="C533" s="6">
-        <v>29.87</v>
+        <v>126</v>
       </c>
       <c r="D533" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>144</v>
-      </c>
-      <c r="B534" s="3" t="s">
-        <v>16</v>
+        <v>229</v>
+      </c>
+      <c r="B534" s="3">
+        <v>4660</v>
       </c>
       <c r="C534" s="6">
-        <v>199</v>
+        <v>20.25</v>
       </c>
       <c r="D534" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>144</v>
-      </c>
-      <c r="B535" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C535" s="6">
-        <v>175</v>
+        <v>229</v>
+      </c>
+      <c r="B535" s="3">
+        <v>6630</v>
       </c>
       <c r="D535" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>144</v>
-      </c>
-      <c r="B536" s="3" t="s">
-        <v>29</v>
+        <v>229</v>
+      </c>
+      <c r="B536" s="3">
+        <v>6642</v>
       </c>
       <c r="C536" s="6">
-        <v>189</v>
+        <v>18.5</v>
       </c>
       <c r="D536" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>144</v>
+        <v>229</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="C537" s="6">
-        <v>309</v>
+        <v>103.5</v>
       </c>
       <c r="D537" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>144</v>
-      </c>
-      <c r="B538" s="3" t="s">
-        <v>212</v>
+        <v>229</v>
+      </c>
+      <c r="B538" s="3">
+        <v>6660</v>
       </c>
       <c r="C538" s="6">
-        <v>175</v>
+        <v>22.5</v>
       </c>
       <c r="D538" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>144</v>
+        <v>229</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>202</v>
+        <v>100</v>
       </c>
       <c r="C539" s="6">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D539" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>144</v>
-      </c>
-      <c r="B540" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C540" s="6">
-        <v>59.99</v>
+        <v>229</v>
+      </c>
+      <c r="B540" s="3">
+        <v>8860</v>
       </c>
       <c r="D540" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A541" t="s">
-        <v>144</v>
-      </c>
-      <c r="B541" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C541" s="6">
-        <v>32.99</v>
-      </c>
-      <c r="D541" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A542" t="s">
-        <v>144</v>
-      </c>
-      <c r="B542" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C542" s="6">
-        <v>129</v>
-      </c>
-      <c r="D542" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>144</v>
+        <v>232</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C543" s="6">
-        <v>149.99</v>
+        <v>233</v>
       </c>
       <c r="D543" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>144</v>
-      </c>
-      <c r="B544" s="3" t="s">
-        <v>59</v>
+        <v>232</v>
+      </c>
+      <c r="B544" s="3">
+        <v>4430</v>
       </c>
       <c r="C544" s="6">
-        <v>47.99</v>
+        <v>15.25</v>
       </c>
       <c r="D544" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>144</v>
-      </c>
-      <c r="B545" s="3" t="s">
-        <v>64</v>
+        <v>232</v>
+      </c>
+      <c r="B545" s="3">
+        <v>4442</v>
       </c>
       <c r="C545" s="6">
-        <v>39.99</v>
+        <v>15</v>
       </c>
       <c r="D545" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>144</v>
+        <v>232</v>
       </c>
       <c r="B546" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C546" s="6">
-        <v>39.99</v>
+        <v>171</v>
       </c>
       <c r="D546" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>144</v>
+        <v>232</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>106</v>
+        <v>97</v>
+      </c>
+      <c r="C547" s="6">
+        <v>972</v>
       </c>
       <c r="D547" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>144</v>
-      </c>
-      <c r="B548" s="3" t="s">
-        <v>278</v>
+        <v>232</v>
+      </c>
+      <c r="B548" s="3">
+        <v>4642</v>
       </c>
       <c r="C548" s="6">
-        <v>36.950000000000003</v>
+        <v>16.5</v>
       </c>
       <c r="D548" t="s">
-        <v>173</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>232</v>
+      </c>
+      <c r="B549" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C549" s="6">
+        <v>126</v>
+      </c>
+      <c r="D549" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>232</v>
+      </c>
+      <c r="B550" s="3">
+        <v>4660</v>
+      </c>
+      <c r="C550" s="6">
+        <v>20.25</v>
+      </c>
+      <c r="D550" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>289</v>
-      </c>
-      <c r="B551" s="3" t="s">
-        <v>8</v>
+        <v>232</v>
+      </c>
+      <c r="B551" s="3">
+        <v>6630</v>
       </c>
       <c r="C551" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D551" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>289</v>
-      </c>
-      <c r="B552" s="3" t="s">
-        <v>9</v>
+        <v>232</v>
+      </c>
+      <c r="B552" s="3">
+        <v>6642</v>
       </c>
       <c r="C552" s="6">
-        <v>100</v>
+        <v>18.5</v>
       </c>
       <c r="D552" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="C553" s="6">
-        <v>99</v>
+        <v>103.5</v>
       </c>
       <c r="D553" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>289</v>
-      </c>
-      <c r="B554" s="3" t="s">
-        <v>11</v>
+        <v>232</v>
+      </c>
+      <c r="B554" s="3">
+        <v>6660</v>
       </c>
       <c r="C554" s="6">
-        <v>134</v>
+        <v>22.5</v>
       </c>
       <c r="D554" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="C555" s="6">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="D555" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>289</v>
-      </c>
-      <c r="B556" s="3" t="s">
-        <v>13</v>
+        <v>232</v>
+      </c>
+      <c r="B556" s="3">
+        <v>8860</v>
       </c>
       <c r="C556" s="6">
-        <v>155</v>
+        <v>42.25</v>
       </c>
       <c r="D556" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>14</v>
+        <v>316</v>
       </c>
       <c r="C557" s="6">
-        <v>239</v>
+        <v>5.75</v>
       </c>
       <c r="D557" t="s">
-        <v>139</v>
+        <v>309</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="C558" s="6">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="D558" t="s">
-        <v>139</v>
+        <v>309</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="C559" s="6">
-        <v>189</v>
+        <v>12.5</v>
       </c>
       <c r="D559" t="s">
-        <v>139</v>
+        <v>309</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="B560" s="3" t="s">
-        <v>19</v>
+        <v>306</v>
       </c>
       <c r="C560" s="6">
-        <v>210</v>
+        <v>77.5</v>
       </c>
       <c r="D560" t="s">
-        <v>139</v>
+        <v>309</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="C561" s="6">
-        <v>285</v>
+        <v>195</v>
       </c>
       <c r="D561" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A562" t="s">
-        <v>289</v>
-      </c>
-      <c r="B562" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C562" s="6">
-        <v>250</v>
-      </c>
-      <c r="D562" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A563" t="s">
-        <v>289</v>
-      </c>
-      <c r="B563" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C563" s="6">
-        <v>19.989999999999998</v>
-      </c>
-      <c r="D563" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A564" t="s">
-        <v>289</v>
-      </c>
-      <c r="B564" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C564" s="6">
-        <v>29.99</v>
-      </c>
-      <c r="D564" t="s">
-        <v>140</v>
+        <v>309</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C565" s="6">
-        <v>155</v>
+        <v>50.35</v>
       </c>
       <c r="D565" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="C566" s="6">
-        <v>190</v>
+        <v>41.99</v>
       </c>
       <c r="D566" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C567" s="6">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="D567" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>29</v>
+        <v>256</v>
       </c>
       <c r="C568" s="6">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="D568" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="C569" s="6">
-        <v>199</v>
+        <v>28.05</v>
       </c>
       <c r="D569" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B570" s="3" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="C570" s="6">
-        <v>260</v>
+        <v>28.05</v>
       </c>
       <c r="D570" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="C571" s="6">
-        <v>399.99</v>
+        <v>28.05</v>
       </c>
       <c r="D571" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="C572" s="6">
-        <v>89.23</v>
+        <v>11.2</v>
       </c>
       <c r="D572" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A573" t="s">
-        <v>289</v>
-      </c>
-      <c r="B573" s="3">
-        <v>6102</v>
-      </c>
-      <c r="C573" s="6">
-        <v>44</v>
-      </c>
-      <c r="D573" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A574" t="s">
-        <v>289</v>
-      </c>
-      <c r="B574" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C574" s="6">
-        <v>64</v>
-      </c>
-      <c r="D574" t="s">
-        <v>269</v>
+        <v>152</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>282</v>
+        <v>4</v>
       </c>
       <c r="C575" s="6">
-        <v>69</v>
+        <v>29.87</v>
       </c>
       <c r="D575" t="s">
-        <v>269</v>
+        <v>136</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>283</v>
+        <v>16</v>
       </c>
       <c r="C576" s="6">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="D576" t="s">
-        <v>269</v>
+        <v>139</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>284</v>
+        <v>28</v>
       </c>
       <c r="C577" s="6">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="D577" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B578" s="3" t="s">
-        <v>285</v>
+        <v>29</v>
       </c>
       <c r="C578" s="6">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="D578" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B579" s="3" t="s">
-        <v>286</v>
+        <v>31</v>
       </c>
       <c r="C579" s="6">
-        <v>114</v>
+        <v>309</v>
       </c>
       <c r="D579" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B580" s="3" t="s">
-        <v>55</v>
+        <v>212</v>
       </c>
       <c r="C580" s="6">
-        <v>27.99</v>
+        <v>175</v>
       </c>
       <c r="D580" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B581" s="3" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="C581" s="6">
-        <v>28.99</v>
+        <v>134</v>
       </c>
       <c r="D581" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C582" s="6">
-        <v>39.99</v>
+        <v>59.99</v>
       </c>
       <c r="D582" t="s">
         <v>145</v>
@@ -9214,13 +9299,13 @@
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>57</v>
+        <v>256</v>
       </c>
       <c r="C583" s="6">
-        <v>58</v>
+        <v>32.99</v>
       </c>
       <c r="D583" t="s">
         <v>145</v>
@@ -9228,13 +9313,13 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="C584" s="6">
-        <v>42.99</v>
+        <v>129</v>
       </c>
       <c r="D584" t="s">
         <v>145</v>
@@ -9242,13 +9327,13 @@
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>58</v>
+        <v>257</v>
       </c>
       <c r="C585" s="6">
-        <v>129</v>
+        <v>149.99</v>
       </c>
       <c r="D585" t="s">
         <v>145</v>
@@ -9256,27 +9341,27 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>257</v>
+        <v>59</v>
       </c>
       <c r="C586" s="6">
-        <v>180</v>
+        <v>47.99</v>
       </c>
       <c r="D586" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C587" s="6">
-        <v>54.5</v>
+        <v>39.99</v>
       </c>
       <c r="D587" t="s">
         <v>146</v>
@@ -9284,192 +9369,192 @@
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C588" s="6">
-        <v>48.99</v>
+        <v>39.99</v>
       </c>
       <c r="D588" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C589" s="6">
-        <v>39.99</v>
+        <v>106</v>
       </c>
       <c r="D589" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>61</v>
+        <v>278</v>
       </c>
       <c r="C590" s="6">
-        <v>64.989999999999995</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="D590" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A591" t="s">
-        <v>289</v>
-      </c>
-      <c r="B591" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C591" s="6">
-        <v>29.99</v>
-      </c>
-      <c r="D591" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A592" t="s">
-        <v>289</v>
-      </c>
-      <c r="B592" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C592" s="6">
-        <v>28.99</v>
-      </c>
-      <c r="D592" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>176</v>
+        <v>8</v>
+      </c>
+      <c r="C593" s="6">
+        <v>18</v>
       </c>
       <c r="D593" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="C594" s="6">
-        <v>29.99</v>
+        <v>100</v>
       </c>
       <c r="D594" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="C595" s="6">
-        <v>25.99</v>
+        <v>99</v>
       </c>
       <c r="D595" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>289</v>
-      </c>
-      <c r="B596" s="3">
-        <v>6642</v>
+        <v>288</v>
+      </c>
+      <c r="B596" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C596" s="6">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="D596" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="C597" s="6">
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="D597" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="C598" s="6">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c r="D598" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B599" s="3" t="s">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="C599" s="6">
-        <v>39.99</v>
+        <v>239</v>
       </c>
       <c r="D599" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B600" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C600" s="6">
+        <v>215</v>
+      </c>
+      <c r="D600" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
         <v>288</v>
       </c>
-      <c r="C600" s="6">
-        <v>90</v>
-      </c>
-      <c r="D600" t="s">
-        <v>154</v>
+      <c r="B601" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C601" s="6">
+        <v>189</v>
+      </c>
+      <c r="D601" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A602" t="s">
+        <v>288</v>
+      </c>
+      <c r="B602" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C602" s="6">
+        <v>210</v>
+      </c>
+      <c r="D602" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="C603" s="6">
-        <v>42.75</v>
+        <v>285</v>
       </c>
       <c r="D603" t="s">
         <v>139</v>
@@ -9477,13 +9562,13 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="C604" s="6">
-        <v>68</v>
+        <v>250</v>
       </c>
       <c r="D604" t="s">
         <v>139</v>
@@ -9491,91 +9576,900 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="C605" s="6">
-        <v>82.2</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D605" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A606" t="s">
+        <v>288</v>
+      </c>
+      <c r="B606" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C606" s="6">
+        <v>29.99</v>
+      </c>
+      <c r="D606" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C607" s="6">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="D607" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="C608" s="6">
+        <v>190</v>
       </c>
       <c r="D608" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>293</v>
-      </c>
-      <c r="B609" s="3">
-        <v>4642</v>
+        <v>288</v>
+      </c>
+      <c r="B609" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C609" s="6">
-        <v>18.96</v>
+        <v>180</v>
       </c>
       <c r="D609" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>293</v>
-      </c>
-      <c r="B610" s="3">
-        <v>6642</v>
+        <v>288</v>
+      </c>
+      <c r="B610" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C610" s="6">
-        <v>22.37</v>
+        <v>170</v>
       </c>
       <c r="D610" t="s">
-        <v>148</v>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
+        <v>288</v>
+      </c>
+      <c r="B611" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C611" s="6">
+        <v>199</v>
+      </c>
+      <c r="D611" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
+        <v>288</v>
+      </c>
+      <c r="B612" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C612" s="6">
+        <v>260</v>
+      </c>
+      <c r="D612" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="C613" s="6">
+        <v>399.99</v>
       </c>
       <c r="D613" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
+        <v>288</v>
+      </c>
+      <c r="B614" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C614" s="6">
+        <v>89.23</v>
+      </c>
+      <c r="D614" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A615" t="s">
+        <v>288</v>
+      </c>
+      <c r="B615" s="3">
+        <v>6102</v>
+      </c>
+      <c r="C615" s="6">
+        <v>44</v>
+      </c>
+      <c r="D615" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A616" t="s">
+        <v>288</v>
+      </c>
+      <c r="B616" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C616" s="6">
+        <v>64</v>
+      </c>
+      <c r="D616" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A617" t="s">
+        <v>288</v>
+      </c>
+      <c r="B617" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C617" s="6">
+        <v>69</v>
+      </c>
+      <c r="D617" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A618" t="s">
+        <v>288</v>
+      </c>
+      <c r="B618" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C618" s="6">
+        <v>72</v>
+      </c>
+      <c r="D618" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A619" t="s">
+        <v>288</v>
+      </c>
+      <c r="B619" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C619" s="6">
+        <v>77</v>
+      </c>
+      <c r="D619" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A620" t="s">
+        <v>288</v>
+      </c>
+      <c r="B620" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C620" s="6">
+        <v>90</v>
+      </c>
+      <c r="D620" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A621" t="s">
+        <v>288</v>
+      </c>
+      <c r="B621" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C621" s="6">
+        <v>114</v>
+      </c>
+      <c r="D621" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A622" t="s">
+        <v>288</v>
+      </c>
+      <c r="B622" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C622" s="6">
+        <v>27.99</v>
+      </c>
+      <c r="D622" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A623" t="s">
+        <v>288</v>
+      </c>
+      <c r="B623" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C623" s="6">
+        <v>28.99</v>
+      </c>
+      <c r="D623" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A624" t="s">
+        <v>288</v>
+      </c>
+      <c r="B624" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C624" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D624" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A625" t="s">
+        <v>288</v>
+      </c>
+      <c r="B625" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C625" s="6">
+        <v>58</v>
+      </c>
+      <c r="D625" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A626" t="s">
+        <v>288</v>
+      </c>
+      <c r="B626" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C626" s="6">
+        <v>42.99</v>
+      </c>
+      <c r="D626" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A627" t="s">
+        <v>288</v>
+      </c>
+      <c r="B627" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C627" s="6">
+        <v>129</v>
+      </c>
+      <c r="D627" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A628" t="s">
+        <v>288</v>
+      </c>
+      <c r="B628" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C628" s="6">
+        <v>180</v>
+      </c>
+      <c r="D628" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A629" t="s">
+        <v>288</v>
+      </c>
+      <c r="B629" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C629" s="6">
+        <v>54.5</v>
+      </c>
+      <c r="D629" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A630" t="s">
+        <v>288</v>
+      </c>
+      <c r="B630" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C630" s="6">
+        <v>48.99</v>
+      </c>
+      <c r="D630" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A631" t="s">
+        <v>288</v>
+      </c>
+      <c r="B631" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C631" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D631" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A632" t="s">
+        <v>288</v>
+      </c>
+      <c r="B632" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C632" s="6">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="D632" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A633" t="s">
+        <v>288</v>
+      </c>
+      <c r="B633" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C633" s="6">
+        <v>29.99</v>
+      </c>
+      <c r="D633" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A634" t="s">
+        <v>288</v>
+      </c>
+      <c r="B634" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C634" s="6">
+        <v>28.99</v>
+      </c>
+      <c r="D634" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A635" t="s">
+        <v>288</v>
+      </c>
+      <c r="B635" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D635" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A636" t="s">
+        <v>288</v>
+      </c>
+      <c r="B636" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C636" s="6">
+        <v>29.99</v>
+      </c>
+      <c r="D636" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A637" t="s">
+        <v>288</v>
+      </c>
+      <c r="B637" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C637" s="6">
+        <v>25.99</v>
+      </c>
+      <c r="D637" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A638" t="s">
+        <v>288</v>
+      </c>
+      <c r="B638" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C638" s="6">
+        <v>50</v>
+      </c>
+      <c r="D638" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A639" t="s">
+        <v>288</v>
+      </c>
+      <c r="B639" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C639" s="6">
+        <v>40</v>
+      </c>
+      <c r="D639" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A640" t="s">
+        <v>288</v>
+      </c>
+      <c r="B640" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C640" s="6">
+        <v>40</v>
+      </c>
+      <c r="D640" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A641" t="s">
+        <v>288</v>
+      </c>
+      <c r="B641" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C641" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D641" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A642" t="s">
+        <v>288</v>
+      </c>
+      <c r="B642" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C642" s="6">
+        <v>90</v>
+      </c>
+      <c r="D642" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A645" t="s">
+        <v>290</v>
+      </c>
+      <c r="B645" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C645" s="6">
+        <v>42.75</v>
+      </c>
+      <c r="D645" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A646" t="s">
+        <v>290</v>
+      </c>
+      <c r="B646" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C646" s="6">
+        <v>68</v>
+      </c>
+      <c r="D646" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A647" t="s">
+        <v>290</v>
+      </c>
+      <c r="B647" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C647" s="6">
+        <v>82.2</v>
+      </c>
+      <c r="D647" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A649" t="s">
+        <v>304</v>
+      </c>
+      <c r="B649" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C649" s="6">
+        <v>10</v>
+      </c>
+      <c r="D649" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A650" t="s">
+        <v>304</v>
+      </c>
+      <c r="B650" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D650" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A651" t="s">
+        <v>304</v>
+      </c>
+      <c r="B651" s="3">
+        <v>4642</v>
+      </c>
+      <c r="C651" s="6">
+        <v>18.96</v>
+      </c>
+      <c r="D651" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A652" t="s">
+        <v>304</v>
+      </c>
+      <c r="B652" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C652" s="6">
+        <v>22.37</v>
+      </c>
+      <c r="D652" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A653" t="s">
+        <v>304</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C653" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D653" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A654" t="s">
+        <v>304</v>
+      </c>
+      <c r="B654" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C654" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D654" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A659" t="s">
+        <v>292</v>
+      </c>
+      <c r="B659" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D659" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A660" t="s">
+        <v>292</v>
+      </c>
+      <c r="B660" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D660" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A664" t="s">
+        <v>293</v>
+      </c>
+      <c r="B664" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C664" s="6">
+        <v>3.15</v>
+      </c>
+      <c r="D664" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A665" t="s">
+        <v>293</v>
+      </c>
+      <c r="B665" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C665" s="6">
+        <v>7.65</v>
+      </c>
+      <c r="D665" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A666" t="s">
+        <v>293</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C666" s="6">
+        <v>8.1</v>
+      </c>
+      <c r="D666" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
+        <v>293</v>
+      </c>
+      <c r="B667" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C667" s="6">
+        <v>10.8</v>
+      </c>
+      <c r="D667" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A668" t="s">
+        <v>293</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C668" s="6">
+        <v>12.2</v>
+      </c>
+      <c r="D668" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A669" t="s">
+        <v>293</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C669" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D669" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A670" t="s">
+        <v>293</v>
+      </c>
+      <c r="B670" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C670" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D670" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A671" t="s">
+        <v>293</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C671" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D671" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A674" t="s">
         <v>294</v>
       </c>
-      <c r="B614" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D614" t="s">
-        <v>140</v>
+      <c r="B674" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C674" s="6">
+        <v>3.36</v>
+      </c>
+      <c r="D674" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A675" t="s">
+        <v>294</v>
+      </c>
+      <c r="B675" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C675" s="6">
+        <v>10.19</v>
+      </c>
+      <c r="D675" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>294</v>
+      </c>
+      <c r="B676" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C676" s="6">
+        <v>14.4</v>
+      </c>
+      <c r="D676" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>294</v>
+      </c>
+      <c r="B677" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C677" s="6">
+        <v>14.39</v>
+      </c>
+      <c r="D677" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>294</v>
+      </c>
+      <c r="B678" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C678" s="6">
+        <v>11.52</v>
+      </c>
+      <c r="D678" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>294</v>
+      </c>
+      <c r="B679" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C679" s="6">
+        <v>12</v>
+      </c>
+      <c r="D679" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>294</v>
+      </c>
+      <c r="B680" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C680" s="6">
+        <v>12</v>
+      </c>
+      <c r="D680" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>294</v>
+      </c>
+      <c r="B681" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C681" s="6">
+        <v>12</v>
+      </c>
+      <c r="D681" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
